--- a/data/67744964-positions.xlsx
+++ b/data/67744964-positions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>代號</t>
   </si>
@@ -133,7 +133,7 @@
     <t>AMD</t>
   </si>
   <si>
-    <t>34,319,236</t>
+    <t>58,211,473</t>
   </si>
   <si>
     <t>04/28/2026</t>
@@ -142,46 +142,46 @@
     <t>-</t>
   </si>
   <si>
-    <t>39,277,121</t>
-  </si>
-  <si>
-    <t>577,939</t>
-  </si>
-  <si>
-    <t>7.78%</t>
+    <t>42,477,588</t>
+  </si>
+  <si>
+    <t>666,035</t>
+  </si>
+  <si>
+    <t>1.44%</t>
   </si>
   <si>
     <t>AMZN</t>
   </si>
   <si>
-    <t>50,878,622</t>
-  </si>
-  <si>
-    <t>48,392,893</t>
-  </si>
-  <si>
-    <t>2,850,522</t>
-  </si>
-  <si>
-    <t>11.50%</t>
+    <t>34,811,892</t>
+  </si>
+  <si>
+    <t>48,597,580</t>
+  </si>
+  <si>
+    <t>2,917,005</t>
+  </si>
+  <si>
+    <t>1.71%</t>
   </si>
   <si>
     <t>CPER</t>
   </si>
   <si>
-    <t>484,442</t>
-  </si>
-  <si>
-    <t>775,264</t>
-  </si>
-  <si>
-    <t>2.35%</t>
+    <t>803,779</t>
+  </si>
+  <si>
+    <t>704,151</t>
+  </si>
+  <si>
+    <t>0.36%</t>
   </si>
   <si>
     <t>GOOG</t>
   </si>
   <si>
-    <t>28,092,462</t>
+    <t>13,786,348</t>
   </si>
   <si>
     <t>05/01/2026</t>
@@ -193,19 +193,46 @@
     <t>06/15/2026</t>
   </si>
   <si>
-    <t>19,948,535</t>
-  </si>
-  <si>
-    <t>4,655,097</t>
-  </si>
-  <si>
-    <t>16.44%</t>
+    <t>19,214,293</t>
+  </si>
+  <si>
+    <t>4,822,047</t>
+  </si>
+  <si>
+    <t>2.48%</t>
+  </si>
+  <si>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>6,739,073</t>
+  </si>
+  <si>
+    <t>1,021.00</t>
+  </si>
+  <si>
+    <t>27,045.00</t>
+  </si>
+  <si>
+    <t>28,683.19</t>
+  </si>
+  <si>
+    <t>-1,638.19</t>
+  </si>
+  <si>
+    <t>5,988,249</t>
+  </si>
+  <si>
+    <t>69,443</t>
+  </si>
+  <si>
+    <t>84.64%</t>
   </si>
   <si>
     <t>MSFT</t>
   </si>
   <si>
-    <t>31,484,887</t>
+    <t>33,516,125</t>
   </si>
   <si>
     <t>05/21/2026</t>
@@ -214,19 +241,19 @@
     <t>06/11/2026</t>
   </si>
   <si>
-    <t>35,343,555</t>
-  </si>
-  <si>
-    <t>3,029,167</t>
-  </si>
-  <si>
-    <t>17.77%</t>
+    <t>34,351,906</t>
+  </si>
+  <si>
+    <t>3,125,662</t>
+  </si>
+  <si>
+    <t>2.60%</t>
   </si>
   <si>
     <t>QQQ</t>
   </si>
   <si>
-    <t>39,206,005</t>
+    <t>44,158,794</t>
   </si>
   <si>
     <t>12/23/2025</t>
@@ -238,82 +265,82 @@
     <t>03/27/2026</t>
   </si>
   <si>
-    <t>54,108,949</t>
-  </si>
-  <si>
-    <t>437,670</t>
-  </si>
-  <si>
-    <t>14.48%</t>
+    <t>48,015,013</t>
+  </si>
+  <si>
+    <t>457,687</t>
+  </si>
+  <si>
+    <t>2.23%</t>
   </si>
   <si>
     <t>SATS</t>
   </si>
   <si>
-    <t>2,394,393</t>
+    <t>3,053,304</t>
   </si>
   <si>
     <t>04/29/2026</t>
   </si>
   <si>
-    <t>7,780,471</t>
-  </si>
-  <si>
-    <t>35,572</t>
-  </si>
-  <si>
-    <t>2.64%</t>
+    <t>5,764,676</t>
+  </si>
+  <si>
+    <t>35,422</t>
+  </si>
+  <si>
+    <t>0.40%</t>
   </si>
   <si>
     <t>SLV</t>
   </si>
   <si>
-    <t>20,237,357</t>
-  </si>
-  <si>
-    <t>33,666,476</t>
-  </si>
-  <si>
-    <t>35,869</t>
-  </si>
-  <si>
-    <t>4.40%</t>
+    <t>19,006,571</t>
+  </si>
+  <si>
+    <t>26,987,853</t>
+  </si>
+  <si>
+    <t>38,240</t>
+  </si>
+  <si>
+    <t>0.68%</t>
   </si>
   <si>
     <t>TSLA</t>
   </si>
   <si>
-    <t>65,684,096</t>
+    <t>65,418,634</t>
   </si>
   <si>
     <t>12/29/2025</t>
   </si>
   <si>
-    <t>67,078,954</t>
-  </si>
-  <si>
-    <t>1,433,297</t>
-  </si>
-  <si>
-    <t>8.41%</t>
+    <t>65,200,875</t>
+  </si>
+  <si>
+    <t>1,546,570</t>
+  </si>
+  <si>
+    <t>1.34%</t>
   </si>
   <si>
     <t>VOO</t>
   </si>
   <si>
-    <t>5,549,214</t>
+    <t>4,458,984</t>
   </si>
   <si>
     <t>03/31/2026</t>
   </si>
   <si>
-    <t>9,241,409</t>
-  </si>
-  <si>
-    <t>877,786</t>
-  </si>
-  <si>
-    <t>14.23%</t>
+    <t>7,089,948</t>
+  </si>
+  <si>
+    <t>885,572</t>
+  </si>
+  <si>
+    <t>2.12%</t>
   </si>
 </sst>
 </file>
@@ -830,22 +857,22 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>361.8502</v>
+        <v>461.2</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3602</v>
+        <v>52.74</v>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>12.91</v>
       </c>
       <c r="G2" t="n">
-        <v>361.81</v>
+        <v>461</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>361.93</v>
+        <v>461.1</v>
       </c>
       <c r="J2" t="n">
         <v>30</v>
@@ -854,28 +881,28 @@
         <v>40</v>
       </c>
       <c r="L2" t="n">
-        <v>354.49</v>
+        <v>408.46</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>362.79</v>
+        <v>456.25</v>
       </c>
       <c r="O2" t="n">
-        <v>349.25</v>
+        <v>418.29</v>
       </c>
       <c r="P2" t="n">
-        <v>354.96</v>
+        <v>430.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>91.87</v>
+        <v>96.88</v>
       </c>
       <c r="R2" t="n">
-        <v>361.85</v>
+        <v>461.2</v>
       </c>
       <c r="S2" t="n">
-        <v>7.36</v>
+        <v>52.74</v>
       </c>
       <c r="T2" t="n">
         <v>322.7</v>
@@ -884,10 +911,10 @@
         <v>322.7</v>
       </c>
       <c r="V2" t="n">
-        <v>39.15</v>
+        <v>138.5</v>
       </c>
       <c r="W2" t="n">
-        <v>12.13</v>
+        <v>42.92</v>
       </c>
       <c r="X2" t="n">
         <v>322.7</v>
@@ -896,10 +923,10 @@
         <v>322.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.15</v>
+        <v>138.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.13</v>
+        <v>42.92</v>
       </c>
       <c r="AB2" t="s">
         <v>41</v>
@@ -917,16 +944,16 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>127.21</v>
+        <v>159.02</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AK2" t="s">
         <v>43</v>
@@ -946,52 +973,52 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>267.5501</v>
+        <v>272.7</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4901</v>
+        <v>1.53</v>
       </c>
       <c r="F3" t="n">
-        <v>0.94</v>
+        <v>0.56</v>
       </c>
       <c r="G3" t="n">
-        <v>267.58</v>
+        <v>272.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>267.8</v>
+        <v>272.7</v>
       </c>
       <c r="J3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="K3" t="s">
         <v>47</v>
       </c>
       <c r="L3" t="n">
-        <v>265.06</v>
+        <v>271.17</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>273.32</v>
+        <v>274</v>
       </c>
       <c r="O3" t="n">
-        <v>262.78</v>
+        <v>269.95</v>
       </c>
       <c r="P3" t="n">
-        <v>273.88</v>
+        <v>278.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>178.85</v>
+        <v>185.01</v>
       </c>
       <c r="R3" t="n">
-        <v>535.1</v>
+        <v>545.4</v>
       </c>
       <c r="S3" t="n">
-        <v>4.98</v>
+        <v>3.06</v>
       </c>
       <c r="T3" t="n">
         <v>236.55</v>
@@ -1000,10 +1027,10 @@
         <v>473.1</v>
       </c>
       <c r="V3" t="n">
-        <v>62</v>
+        <v>72.3</v>
       </c>
       <c r="W3" t="n">
-        <v>13.11</v>
+        <v>15.28</v>
       </c>
       <c r="X3" t="n">
         <v>473.1</v>
@@ -1012,10 +1039,10 @@
         <v>236.55</v>
       </c>
       <c r="Z3" t="n">
-        <v>62</v>
+        <v>72.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.11</v>
+        <v>15.28</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1030,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.17</v>
+        <v>8.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>36.69</v>
+        <v>38.35</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AK3" t="s">
         <v>48</v>
@@ -1059,22 +1086,22 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>36.4</v>
+        <v>38.27</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.13</v>
+        <v>0.92</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.36</v>
+        <v>2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>32.95</v>
+        <v>32.4</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>39.67</v>
+        <v>38.37</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -1083,16 +1110,16 @@
         <v>52</v>
       </c>
       <c r="L4" t="n">
-        <v>36.53</v>
+        <v>37.35</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>36.49</v>
+        <v>38.35</v>
       </c>
       <c r="O4" t="n">
-        <v>36.2</v>
+        <v>38.01</v>
       </c>
       <c r="P4" t="n">
         <v>40.44</v>
@@ -1101,10 +1128,10 @@
         <v>27.08</v>
       </c>
       <c r="R4" t="n">
-        <v>109.2</v>
+        <v>114.81</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.39</v>
+        <v>2.76</v>
       </c>
       <c r="T4" t="n">
         <v>36.69</v>
@@ -1113,10 +1140,10 @@
         <v>110.07</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.87</v>
+        <v>4.74</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.79</v>
+        <v>4.31</v>
       </c>
       <c r="X4" t="n">
         <v>110.07</v>
@@ -1125,10 +1152,10 @@
         <v>36.69</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.87</v>
+        <v>4.74</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.79</v>
+        <v>4.31</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1152,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="AK4" t="s">
         <v>53</v>
       </c>
       <c r="AL4" t="n">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="AM4" t="s">
         <v>54</v>
@@ -1172,52 +1199,52 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>382.45</v>
+        <v>395.7999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.51</v>
+        <v>0.4999</v>
       </c>
       <c r="F5" t="n">
         <v>0.13</v>
       </c>
       <c r="G5" t="n">
-        <v>382.41</v>
+        <v>395.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>388.71</v>
+        <v>395.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K5" t="s">
         <v>56</v>
       </c>
       <c r="L5" t="n">
-        <v>381.94</v>
+        <v>395.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>383.39</v>
+        <v>398.37</v>
       </c>
       <c r="O5" t="n">
-        <v>375.27</v>
+        <v>393.68</v>
       </c>
       <c r="P5" t="n">
-        <v>382.63</v>
+        <v>397.36</v>
       </c>
       <c r="Q5" t="n">
         <v>149.49</v>
       </c>
       <c r="R5" t="n">
-        <v>764.9</v>
+        <v>791.6</v>
       </c>
       <c r="S5" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>379.19</v>
@@ -1226,10 +1253,10 @@
         <v>758.38</v>
       </c>
       <c r="V5" t="n">
-        <v>6.52</v>
+        <v>33.22</v>
       </c>
       <c r="W5" t="n">
-        <v>0.86</v>
+        <v>4.38</v>
       </c>
       <c r="X5" t="n">
         <v>758.38</v>
@@ -1238,10 +1265,10 @@
         <v>379.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.52</v>
+        <v>33.22</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.86</v>
+        <v>4.38</v>
       </c>
       <c r="AB5" t="s">
         <v>57</v>
@@ -1262,13 +1289,13 @@
         <v>13.11</v>
       </c>
       <c r="AH5" t="n">
-        <v>32.13</v>
+        <v>36.55</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK5" t="s">
         <v>60</v>
@@ -1285,424 +1312,424 @@
         <v>63</v>
       </c>
       <c r="B6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="n">
+        <v>901.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>900</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>901.4</v>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>413.2416</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5.4616</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>418.29</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
       </c>
       <c r="K6" t="s">
         <v>64</v>
       </c>
       <c r="L6" t="n">
-        <v>407.78</v>
+        <v>892.58</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>417.11</v>
+        <v>934.92</v>
       </c>
       <c r="O6" t="n">
-        <v>410.43</v>
-      </c>
-      <c r="P6" t="n">
-        <v>555.45</v>
+        <v>866</v>
+      </c>
+      <c r="P6" t="s">
+        <v>65</v>
       </c>
       <c r="Q6" t="n">
-        <v>356.28</v>
-      </c>
-      <c r="R6" t="n">
-        <v>826.48</v>
+        <v>60.38</v>
+      </c>
+      <c r="R6" t="s">
+        <v>66</v>
       </c>
       <c r="S6" t="n">
-        <v>10.92</v>
+        <v>267.6</v>
       </c>
       <c r="T6" t="n">
-        <v>386.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>773</v>
-      </c>
-      <c r="V6" t="n">
-        <v>53.48</v>
+        <v>956.10633</v>
+      </c>
+      <c r="U6" t="s">
+        <v>67</v>
+      </c>
+      <c r="V6" t="s">
+        <v>68</v>
       </c>
       <c r="W6" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="X6" t="n">
-        <v>773</v>
+        <v>-5.71</v>
+      </c>
+      <c r="X6" t="s">
+        <v>67</v>
       </c>
       <c r="Y6" t="n">
-        <v>386.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>53.48</v>
+        <v>956.11</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>68</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.92</v>
+        <v>-5.71</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AE6" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>16.8</v>
+        <v>3.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>26.55</v>
+        <v>277.73</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AK6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AL6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>673.5501</v>
+        <v>415.0953</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8101</v>
+        <v>-5.6747</v>
       </c>
       <c r="F7" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="G7" t="n">
+        <v>415.06</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>418.95</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K7" t="s">
+        <v>73</v>
+      </c>
+      <c r="L7" t="n">
+        <v>420.77</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>418.63</v>
+      </c>
+      <c r="O7" t="n">
+        <v>414</v>
+      </c>
+      <c r="P7" t="n">
+        <v>555.45</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="R7" t="n">
+        <v>830.19</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-11.35</v>
+      </c>
+      <c r="T7" t="n">
+        <v>386.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>773</v>
+      </c>
+      <c r="V7" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>386.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.87</v>
       </c>
-      <c r="G7" t="n">
-        <v>673.52</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>673.76</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>71</v>
-      </c>
-      <c r="L7" t="n">
-        <v>667.74</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>675.97</v>
-      </c>
-      <c r="O7" t="n">
-        <v>668.8</v>
-      </c>
-      <c r="P7" t="n">
-        <v>668.9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>462.43</v>
-      </c>
-      <c r="R7" t="n">
-        <v>673.55</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="T7" t="n">
-        <v>619.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>619.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="W7" t="n">
-        <v>8.72</v>
-      </c>
-      <c r="X7" t="n">
-        <v>619.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>619.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>8.72</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>33.49</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.42</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AK7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>123</v>
+        <v>712.105</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.14</v>
+        <v>17.165</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.11</v>
+        <v>2.47</v>
       </c>
       <c r="G8" t="n">
-        <v>119.28</v>
+        <v>711</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I8" t="n">
-        <v>127.07</v>
+        <v>712.08</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L8" t="n">
-        <v>123.14</v>
+        <v>694.94</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>124.34</v>
+        <v>711.14</v>
       </c>
       <c r="O8" t="n">
-        <v>121.56</v>
+        <v>699.53</v>
       </c>
       <c r="P8" t="n">
-        <v>137.44</v>
+        <v>701.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.9</v>
+        <v>476.78</v>
       </c>
       <c r="R8" t="n">
-        <v>123</v>
+        <v>712.11</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.14</v>
+        <v>17.17</v>
       </c>
       <c r="T8" t="n">
-        <v>122.27</v>
+        <v>619.5</v>
       </c>
       <c r="U8" t="n">
-        <v>122.27</v>
+        <v>619.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0.73</v>
+        <v>92.61</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6</v>
+        <v>14.95</v>
       </c>
       <c r="X8" t="n">
-        <v>122.27</v>
+        <v>619.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>122.27</v>
+        <v>619.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.73</v>
+        <v>92.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6</v>
+        <v>14.95</v>
       </c>
       <c r="AB8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD8" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="AE8" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>33.49</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AM8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>68.1896</v>
+        <v>127.7</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5296</v>
+        <v>5.08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.29</v>
+        <v>4.14</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>127.25</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>70</v>
+        <v>133.5</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L9" t="n">
-        <v>66.66</v>
+        <v>122.62</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>69.65</v>
+        <v>127.25</v>
       </c>
       <c r="O9" t="n">
-        <v>67.51</v>
+        <v>122.63</v>
       </c>
       <c r="P9" t="n">
-        <v>109.83</v>
+        <v>137.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>29.04</v>
+        <v>14.9</v>
       </c>
       <c r="R9" t="n">
-        <v>204.57</v>
+        <v>127.7</v>
       </c>
       <c r="S9" t="n">
-        <v>4.59</v>
+        <v>5.08</v>
       </c>
       <c r="T9" t="n">
-        <v>74.94667</v>
+        <v>122.27</v>
       </c>
       <c r="U9" t="n">
-        <v>224.84</v>
+        <v>122.27</v>
       </c>
       <c r="V9" t="n">
-        <v>-20.27</v>
+        <v>5.43</v>
       </c>
       <c r="W9" t="n">
-        <v>-9.02</v>
+        <v>4.44</v>
       </c>
       <c r="X9" t="n">
-        <v>224.84</v>
+        <v>122.27</v>
       </c>
       <c r="Y9" t="n">
-        <v>74.95</v>
+        <v>122.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>-20.27</v>
+        <v>5.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>-9.02</v>
+        <v>4.44</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>89</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1726,99 +1753,96 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.53</v>
+        <v>0.96</v>
       </c>
       <c r="AK9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AL9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AM9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>72.78</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G10" t="n">
+        <v>72.78</v>
+      </c>
+      <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
-        <v>391.34</v>
-      </c>
-      <c r="E10" t="n">
-        <v>9.71</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="G10" t="n">
-        <v>186.91</v>
-      </c>
-      <c r="H10" t="n">
-        <v>10</v>
-      </c>
       <c r="I10" t="n">
-        <v>391.34</v>
+        <v>73.99</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L10" t="n">
-        <v>381.63</v>
+        <v>71.6</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>397.82</v>
+        <v>73.83</v>
       </c>
       <c r="O10" t="n">
-        <v>378.91</v>
+        <v>72.29</v>
       </c>
       <c r="P10" t="n">
-        <v>498.83</v>
+        <v>109.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>270.78</v>
+        <v>29.1</v>
       </c>
       <c r="R10" t="n">
-        <v>391.34</v>
+        <v>218.34</v>
       </c>
       <c r="S10" t="n">
-        <v>9.71</v>
+        <v>3.54</v>
       </c>
       <c r="T10" t="n">
-        <v>468.88</v>
+        <v>74.94667</v>
       </c>
       <c r="U10" t="n">
-        <v>468.88</v>
+        <v>224.84</v>
       </c>
       <c r="V10" t="n">
-        <v>-77.54</v>
+        <v>-6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>-16.54</v>
+        <v>-2.89</v>
       </c>
       <c r="X10" t="n">
-        <v>468.88</v>
+        <v>224.84</v>
       </c>
       <c r="Y10" t="n">
-        <v>468.88</v>
+        <v>74.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>-77.54</v>
+        <v>-6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>-16.54</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>91</v>
+        <v>-2.89</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1833,141 +1857,257 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>342.02</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.92</v>
+        <v>0.45</v>
       </c>
       <c r="AK10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AL10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AM10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>661.95</v>
+        <v>427.98</v>
       </c>
       <c r="E11" t="n">
-        <v>1.37</v>
+        <v>16.19</v>
       </c>
       <c r="F11" t="n">
-        <v>0.21</v>
+        <v>3.93</v>
       </c>
       <c r="G11" t="n">
-        <v>660.5</v>
+        <v>427.98</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>697</v>
+        <v>428</v>
       </c>
       <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" t="n">
+        <v>411.79</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>431.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>416.39</v>
+      </c>
+      <c r="P11" t="n">
+        <v>498.83</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>271</v>
+      </c>
+      <c r="R11" t="n">
+        <v>427.98</v>
+      </c>
+      <c r="S11" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="T11" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="U11" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-40.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-8.72</v>
+      </c>
+      <c r="X11" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-40.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-8.72</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>365.81</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>101</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" collapsed="0" hidden="0" customHeight="0" spans="1:1">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="s">
-        <v>96</v>
-      </c>
-      <c r="L11" t="n">
-        <v>660.58</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>666.41</v>
-      </c>
-      <c r="O11" t="n">
-        <v>662.42</v>
-      </c>
-      <c r="P11" t="n">
-        <v>661.77</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>497.76</v>
-      </c>
-      <c r="R11" t="n">
-        <v>661.95</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="D12" t="n">
+        <v>678.425</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.885</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G12" t="n">
+        <v>677.98</v>
+      </c>
+      <c r="H12" t="n">
+        <v>199</v>
+      </c>
+      <c r="I12" t="n">
+        <v>688</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>105</v>
+      </c>
+      <c r="L12" t="n">
+        <v>672.54</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>678.51</v>
+      </c>
+      <c r="O12" t="n">
+        <v>675.43</v>
+      </c>
+      <c r="P12" t="n">
+        <v>676.76</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>511.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>678.43</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="T12" t="n">
         <v>629.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>629.5</v>
       </c>
-      <c r="V11" t="n">
-        <v>32.45</v>
-      </c>
-      <c r="W11" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="V12" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="X12" t="n">
         <v>629.5</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y12" t="n">
         <v>629.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>32.45</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="Z12" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC12" t="n">
         <v>7.13</v>
       </c>
-      <c r="AD11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AD12" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF12" t="n">
         <v>7.13</v>
       </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
         <v>26.2</v>
       </c>
-      <c r="AI11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="AI12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1</v>
       </c>
-      <c r="AK11" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>99</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>100</v>
+      <c r="AK12" t="s">
+        <v>107</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/67744964-positions.xlsx
+++ b/data/67744964-positions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>代號</t>
   </si>
@@ -22,6 +22,9 @@
     <t>行动</t>
   </si>
   <si>
+    <t>詳細說明</t>
+  </si>
+  <si>
     <t>價格</t>
   </si>
   <si>
@@ -133,7 +136,10 @@
     <t>AMD</t>
   </si>
   <si>
-    <t>58,211,473</t>
+    <t>Advanced Micro Devices Inc.</t>
+  </si>
+  <si>
+    <t>1,134,024</t>
   </si>
   <si>
     <t>04/28/2026</t>
@@ -142,46 +148,58 @@
     <t>-</t>
   </si>
   <si>
-    <t>42,477,588</t>
-  </si>
-  <si>
-    <t>666,035</t>
-  </si>
-  <si>
-    <t>1.44%</t>
+    <t>42,878,903</t>
+  </si>
+  <si>
+    <t>726,433</t>
+  </si>
+  <si>
+    <t>1.35%</t>
   </si>
   <si>
     <t>AMZN</t>
   </si>
   <si>
-    <t>34,811,892</t>
-  </si>
-  <si>
-    <t>48,597,580</t>
-  </si>
-  <si>
-    <t>2,917,005</t>
-  </si>
-  <si>
-    <t>1.71%</t>
+    <t>Amazon.com Inc.</t>
+  </si>
+  <si>
+    <t>380,105</t>
+  </si>
+  <si>
+    <t>46,600,610</t>
+  </si>
+  <si>
+    <t>2,905,818</t>
+  </si>
+  <si>
+    <t>1.67%</t>
   </si>
   <si>
     <t>CPER</t>
   </si>
   <si>
-    <t>803,779</t>
-  </si>
-  <si>
-    <t>704,151</t>
-  </si>
-  <si>
-    <t>0.36%</t>
+    <t>United States Copper Index Fund</t>
+  </si>
+  <si>
+    <t>1,000</t>
+  </si>
+  <si>
+    <t>29,633</t>
+  </si>
+  <si>
+    <t>800,928</t>
+  </si>
+  <si>
+    <t>0.37%</t>
   </si>
   <si>
     <t>GOOG</t>
   </si>
   <si>
-    <t>13,786,348</t>
+    <t>Alphabet Inc.</t>
+  </si>
+  <si>
+    <t>268,768</t>
   </si>
   <si>
     <t>05/01/2026</t>
@@ -193,46 +211,91 @@
     <t>06/15/2026</t>
   </si>
   <si>
-    <t>19,214,293</t>
-  </si>
-  <si>
-    <t>4,822,047</t>
-  </si>
-  <si>
-    <t>2.48%</t>
+    <t>17,747,786</t>
+  </si>
+  <si>
+    <t>4,878,144</t>
+  </si>
+  <si>
+    <t>2.46%</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>Intel Corporation</t>
+  </si>
+  <si>
+    <t>1,344</t>
+  </si>
+  <si>
+    <t>6,254,824</t>
+  </si>
+  <si>
+    <t>05/12/2026</t>
+  </si>
+  <si>
+    <t>144,227,256</t>
+  </si>
+  <si>
+    <t>604,578</t>
+  </si>
+  <si>
+    <t>0.72%</t>
   </si>
   <si>
     <t>LITE</t>
   </si>
   <si>
-    <t>6,739,073</t>
-  </si>
-  <si>
-    <t>1,021.00</t>
-  </si>
-  <si>
-    <t>27,045.00</t>
-  </si>
-  <si>
-    <t>28,683.19</t>
-  </si>
-  <si>
-    <t>-1,638.19</t>
-  </si>
-  <si>
-    <t>5,988,249</t>
-  </si>
-  <si>
-    <t>69,443</t>
-  </si>
-  <si>
-    <t>84.64%</t>
+    <t>Lumentum Holdings Inc.</t>
+  </si>
+  <si>
+    <t>1,014.01</t>
+  </si>
+  <si>
+    <t>1,013.00</t>
+  </si>
+  <si>
+    <t>1,017.45</t>
+  </si>
+  <si>
+    <t>105,983</t>
+  </si>
+  <si>
+    <t>1,030.37</t>
+  </si>
+  <si>
+    <t>1,085.68</t>
+  </si>
+  <si>
+    <t>20,280.20</t>
+  </si>
+  <si>
+    <t>1,023.848</t>
+  </si>
+  <si>
+    <t>20,476.96</t>
+  </si>
+  <si>
+    <t>1,023.85</t>
+  </si>
+  <si>
+    <t>6,092,637</t>
+  </si>
+  <si>
+    <t>80,163</t>
+  </si>
+  <si>
+    <t>62.94%</t>
   </si>
   <si>
     <t>MSFT</t>
   </si>
   <si>
-    <t>33,516,125</t>
+    <t>Microsoft Corporation</t>
+  </si>
+  <si>
+    <t>485,646</t>
   </si>
   <si>
     <t>05/21/2026</t>
@@ -241,19 +304,52 @@
     <t>06/11/2026</t>
   </si>
   <si>
-    <t>34,351,906</t>
-  </si>
-  <si>
-    <t>3,125,662</t>
-  </si>
-  <si>
-    <t>2.60%</t>
+    <t>33,407,786</t>
+  </si>
+  <si>
+    <t>3,010,076</t>
+  </si>
+  <si>
+    <t>2.52%</t>
+  </si>
+  <si>
+    <t>MU</t>
+  </si>
+  <si>
+    <t>Micron Technology Inc.</t>
+  </si>
+  <si>
+    <t>1,983,537</t>
+  </si>
+  <si>
+    <t>3,981.30</t>
+  </si>
+  <si>
+    <t>3,726.86</t>
+  </si>
+  <si>
+    <t>03/30/2026</t>
+  </si>
+  <si>
+    <t>04/15/2026</t>
+  </si>
+  <si>
+    <t>46,296,949</t>
+  </si>
+  <si>
+    <t>906,281</t>
+  </si>
+  <si>
+    <t>12.36%</t>
   </si>
   <si>
     <t>QQQ</t>
   </si>
   <si>
-    <t>44,158,794</t>
+    <t>INVESCO QQQ Trust</t>
+  </si>
+  <si>
+    <t>1,117,521</t>
   </si>
   <si>
     <t>12/23/2025</t>
@@ -265,79 +361,133 @@
     <t>03/27/2026</t>
   </si>
   <si>
-    <t>48,015,013</t>
-  </si>
-  <si>
-    <t>457,687</t>
-  </si>
-  <si>
-    <t>2.23%</t>
+    <t>42,551,499</t>
+  </si>
+  <si>
+    <t>466,777</t>
+  </si>
+  <si>
+    <t>2.22%</t>
   </si>
   <si>
     <t>SATS</t>
   </si>
   <si>
-    <t>3,053,304</t>
+    <t>EchoStar Corporation</t>
+  </si>
+  <si>
+    <t>30,093</t>
   </si>
   <si>
     <t>04/29/2026</t>
   </si>
   <si>
-    <t>5,764,676</t>
-  </si>
-  <si>
-    <t>35,422</t>
-  </si>
-  <si>
-    <t>0.40%</t>
+    <t>5,342,680</t>
+  </si>
+  <si>
+    <t>38,612</t>
+  </si>
+  <si>
+    <t>0.42%</t>
   </si>
   <si>
     <t>SLV</t>
   </si>
   <si>
-    <t>19,006,571</t>
-  </si>
-  <si>
-    <t>26,987,853</t>
-  </si>
-  <si>
-    <t>38,240</t>
-  </si>
-  <si>
-    <t>0.68%</t>
+    <t>iShares Silver Trust</t>
+  </si>
+  <si>
+    <t>2,800</t>
+  </si>
+  <si>
+    <t>2,583,891</t>
+  </si>
+  <si>
+    <t>24,934,175</t>
+  </si>
+  <si>
+    <t>42,416</t>
+  </si>
+  <si>
+    <t>SNDK</t>
+  </si>
+  <si>
+    <t>Sandisk Corporation</t>
+  </si>
+  <si>
+    <t>1,406.48</t>
+  </si>
+  <si>
+    <t>1,405.42</t>
+  </si>
+  <si>
+    <t>1,407.19</t>
+  </si>
+  <si>
+    <t>524,453</t>
+  </si>
+  <si>
+    <t>1,447.23</t>
+  </si>
+  <si>
+    <t>1,600.00</t>
+  </si>
+  <si>
+    <t>2,812.96</t>
+  </si>
+  <si>
+    <t>1,435.05</t>
+  </si>
+  <si>
+    <t>2,870.10</t>
+  </si>
+  <si>
+    <t>16,315,380</t>
+  </si>
+  <si>
+    <t>214,320</t>
+  </si>
+  <si>
+    <t>8.73%</t>
   </si>
   <si>
     <t>TSLA</t>
   </si>
   <si>
-    <t>65,418,634</t>
+    <t>Tesla Inc.</t>
+  </si>
+  <si>
+    <t>1,579,745</t>
   </si>
   <si>
     <t>12/29/2025</t>
   </si>
   <si>
-    <t>65,200,875</t>
-  </si>
-  <si>
-    <t>1,546,570</t>
-  </si>
-  <si>
-    <t>1.34%</t>
+    <t>65,549,500</t>
+  </si>
+  <si>
+    <t>1,672,311</t>
+  </si>
+  <si>
+    <t>1.39%</t>
   </si>
   <si>
     <t>VOO</t>
   </si>
   <si>
-    <t>4,458,984</t>
+    <t>Vanguard S&amp;P 500 ETF</t>
+  </si>
+  <si>
+    <t>94,275</t>
   </si>
   <si>
     <t>03/31/2026</t>
   </si>
   <si>
-    <t>7,089,948</t>
-  </si>
-  <si>
-    <t>885,572</t>
+    <t>6,336,641</t>
+  </si>
+  <si>
+    <t>933,607</t>
   </si>
   <si>
     <t>2.12%</t>
@@ -692,10 +842,10 @@
     <col min="1" max="1" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="2" max="2" width="14" hidden="0" bestFit="0" customWidth="1"/>
     <col min="3" max="3" width="10" hidden="0" bestFit="0" customWidth="1"/>
-    <col min="4" max="4" width="14" hidden="0" bestFit="0" customWidth="1"/>
+    <col min="4" max="4" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="5" max="5" width="14" hidden="0" bestFit="0" customWidth="1"/>
     <col min="6" max="6" width="14" hidden="0" bestFit="0" customWidth="1"/>
-    <col min="7" max="7" width="28" hidden="0" bestFit="0" customWidth="1"/>
+    <col min="7" max="7" width="14" hidden="0" bestFit="0" customWidth="1"/>
     <col min="8" max="8" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="9" max="9" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="10" max="10" width="28" hidden="0" bestFit="0" customWidth="1"/>
@@ -706,13 +856,13 @@
     <col min="15" max="15" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="16" max="16" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="17" max="17" width="28" hidden="0" bestFit="0" customWidth="1"/>
-    <col min="18" max="18" width="14" hidden="0" bestFit="0" customWidth="1"/>
+    <col min="18" max="18" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="19" max="19" width="14" hidden="0" bestFit="0" customWidth="1"/>
     <col min="20" max="20" width="14" hidden="0" bestFit="0" customWidth="1"/>
     <col min="21" max="21" width="14" hidden="0" bestFit="0" customWidth="1"/>
     <col min="22" max="22" width="14" hidden="0" bestFit="0" customWidth="1"/>
     <col min="23" max="23" width="14" hidden="0" bestFit="0" customWidth="1"/>
-    <col min="24" max="24" width="28" hidden="0" bestFit="0" customWidth="1"/>
+    <col min="24" max="24" width="14" hidden="0" bestFit="0" customWidth="1"/>
     <col min="25" max="25" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="26" max="26" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="27" max="27" width="28" hidden="0" bestFit="0" customWidth="1"/>
@@ -727,7 +877,8 @@
     <col min="36" max="36" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="37" max="37" width="28" hidden="0" bestFit="0" customWidth="1"/>
     <col min="38" max="38" width="28" hidden="0" bestFit="0" customWidth="1"/>
-    <col min="39" max="39" width="17" hidden="0" bestFit="0" customWidth="1"/>
+    <col min="39" max="39" width="28" hidden="0" bestFit="0" customWidth="1"/>
+    <col min="40" max="40" width="17" hidden="0" bestFit="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" collapsed="0" hidden="0" customHeight="0" spans="1:1">
@@ -740,7 +891,7 @@
       <c r="C1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="3">
+      <c r="D1" t="s" s="4">
         <v>3</v>
       </c>
       <c r="E1" t="s" s="3">
@@ -812,19 +963,19 @@
       <c r="AA1" t="s" s="3">
         <v>26</v>
       </c>
-      <c r="AB1" t="s" s="4">
+      <c r="AB1" t="s" s="3">
         <v>27</v>
       </c>
-      <c r="AC1" t="s" s="3">
+      <c r="AC1" t="s" s="4">
         <v>28</v>
       </c>
-      <c r="AD1" t="s" s="4">
+      <c r="AD1" t="s" s="3">
         <v>29</v>
       </c>
       <c r="AE1" t="s" s="4">
         <v>30</v>
       </c>
-      <c r="AF1" t="s" s="3">
+      <c r="AF1" t="s" s="4">
         <v>31</v>
       </c>
       <c r="AG1" t="s" s="3">
@@ -847,327 +998,336 @@
       </c>
       <c r="AM1" t="s" s="3">
         <v>38</v>
+      </c>
+      <c r="AN1" t="s" s="3">
+        <v>39</v>
       </c>
     </row>
     <row r="2" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>461.2</v>
+      <c r="D2" t="s">
+        <v>41</v>
       </c>
       <c r="E2" t="n">
-        <v>52.74</v>
+        <v>435.9536</v>
       </c>
       <c r="F2" t="n">
-        <v>12.91</v>
+        <v>-9.5464</v>
       </c>
       <c r="G2" t="n">
-        <v>461</v>
+        <v>-2.14</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>435.7</v>
       </c>
       <c r="I2" t="n">
-        <v>461.1</v>
+        <v>58</v>
       </c>
       <c r="J2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L2" t="n">
-        <v>408.46</v>
+        <v>435.99</v>
+      </c>
+      <c r="K2" t="n">
+        <v>120</v>
+      </c>
+      <c r="L2" t="s">
+        <v>42</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>445.5</v>
       </c>
       <c r="N2" t="n">
-        <v>456.25</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>418.29</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>430.6</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>96.88</v>
+        <v>469.22</v>
       </c>
       <c r="R2" t="n">
-        <v>461.2</v>
+        <v>107.67</v>
       </c>
       <c r="S2" t="n">
-        <v>52.74</v>
+        <v>435.95</v>
       </c>
       <c r="T2" t="n">
-        <v>322.7</v>
+        <v>-9.55</v>
       </c>
       <c r="U2" t="n">
         <v>322.7</v>
       </c>
       <c r="V2" t="n">
-        <v>138.5</v>
+        <v>322.7</v>
       </c>
       <c r="W2" t="n">
-        <v>42.92</v>
+        <v>113.25</v>
       </c>
       <c r="X2" t="n">
-        <v>322.7</v>
+        <v>35.1</v>
       </c>
       <c r="Y2" t="n">
         <v>322.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>138.5</v>
+        <v>322.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>42.92</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>42</v>
+        <v>113.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
       </c>
       <c r="AE2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>44</v>
       </c>
       <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>3.05</v>
       </c>
-      <c r="AH2" t="n">
-        <v>159.02</v>
-      </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>146.98</v>
       </c>
       <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
         <v>2.4</v>
       </c>
-      <c r="AK2" t="s">
-        <v>43</v>
-      </c>
       <c r="AL2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AM2" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>272.7</v>
+      <c r="D3" t="s">
+        <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>1.53</v>
+        <v>269</v>
       </c>
       <c r="F3" t="n">
-        <v>0.56</v>
+        <v>-1.13</v>
       </c>
       <c r="G3" t="n">
-        <v>272.5</v>
+        <v>-0.42</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>269</v>
       </c>
       <c r="I3" t="n">
-        <v>272.7</v>
+        <v>144</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L3" t="n">
-        <v>271.17</v>
+        <v>269.12</v>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" t="s">
+        <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>270.13</v>
       </c>
       <c r="N3" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>269.95</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>278.56</v>
       </c>
-      <c r="Q3" t="n">
-        <v>185.01</v>
-      </c>
       <c r="R3" t="n">
-        <v>545.4</v>
+        <v>196</v>
       </c>
       <c r="S3" t="n">
-        <v>3.06</v>
+        <v>538</v>
       </c>
       <c r="T3" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="U3" t="n">
         <v>236.55</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>473.1</v>
       </c>
-      <c r="V3" t="n">
-        <v>72.3</v>
-      </c>
       <c r="W3" t="n">
-        <v>15.28</v>
+        <v>64.9</v>
       </c>
       <c r="X3" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="Y3" t="n">
         <v>473.1</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>236.55</v>
       </c>
-      <c r="Z3" t="n">
-        <v>72.3</v>
-      </c>
       <c r="AA3" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>42</v>
+        <v>64.9</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
       </c>
       <c r="AE3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>44</v>
       </c>
       <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>8.36</v>
       </c>
-      <c r="AH3" t="n">
-        <v>38.35</v>
-      </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>37.07</v>
       </c>
       <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.47</v>
       </c>
-      <c r="AK3" t="s">
-        <v>48</v>
-      </c>
       <c r="AL3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AM3" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>38.27</v>
+      <c r="D4" t="s">
+        <v>55</v>
       </c>
       <c r="E4" t="n">
-        <v>0.92</v>
+        <v>40.19</v>
       </c>
       <c r="F4" t="n">
-        <v>2.46</v>
+        <v>-0.08</v>
       </c>
       <c r="G4" t="n">
-        <v>32.4</v>
+        <v>-0.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>40.11</v>
       </c>
       <c r="I4" t="n">
-        <v>38.37</v>
+        <v>800</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>40.26</v>
       </c>
       <c r="K4" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" t="n">
-        <v>37.35</v>
+        <v>56</v>
+      </c>
+      <c r="L4" t="s">
+        <v>57</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>40.27</v>
       </c>
       <c r="N4" t="n">
-        <v>38.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>38.01</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>40.44</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="R4" t="n">
         <v>27.08</v>
       </c>
-      <c r="R4" t="n">
-        <v>114.81</v>
-      </c>
       <c r="S4" t="n">
-        <v>2.76</v>
+        <v>120.57</v>
       </c>
       <c r="T4" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="U4" t="n">
         <v>36.69</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>110.07</v>
       </c>
-      <c r="V4" t="n">
-        <v>4.74</v>
-      </c>
       <c r="W4" t="n">
-        <v>4.31</v>
+        <v>10.5</v>
       </c>
       <c r="X4" t="n">
+        <v>9.54</v>
+      </c>
+      <c r="Y4" t="n">
         <v>110.07</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>36.69</v>
       </c>
-      <c r="Z4" t="n">
-        <v>4.74</v>
-      </c>
       <c r="AA4" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>42</v>
+        <v>10.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.54</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
       </c>
       <c r="AE4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>44</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1179,935 +1339,1313 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0.46</v>
       </c>
-      <c r="AK4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>721</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>54</v>
+      <c r="AL4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>775</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
-        <v>395.7999</v>
+      <c r="D5" t="s">
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4999</v>
+        <v>396.37</v>
       </c>
       <c r="F5" t="n">
-        <v>0.13</v>
+        <v>-2.67</v>
       </c>
       <c r="G5" t="n">
-        <v>395.5</v>
+        <v>-0.67</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>396.29</v>
       </c>
       <c r="I5" t="n">
-        <v>395.8</v>
+        <v>120</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K5" t="s">
-        <v>56</v>
-      </c>
-      <c r="L5" t="n">
-        <v>395.3</v>
+        <v>396.46</v>
+      </c>
+      <c r="K5" t="n">
+        <v>120</v>
+      </c>
+      <c r="L5" t="s">
+        <v>62</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>399.04</v>
       </c>
       <c r="N5" t="n">
-        <v>398.37</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>393.68</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>397.36</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>149.49</v>
+        <v>399.93</v>
       </c>
       <c r="R5" t="n">
-        <v>791.6</v>
+        <v>157.58</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>792.74</v>
       </c>
       <c r="T5" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="U5" t="n">
         <v>379.19</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>758.38</v>
       </c>
-      <c r="V5" t="n">
-        <v>33.22</v>
-      </c>
       <c r="W5" t="n">
-        <v>4.38</v>
+        <v>34.36</v>
       </c>
       <c r="X5" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="Y5" t="n">
         <v>758.38</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>379.19</v>
       </c>
-      <c r="Z5" t="n">
-        <v>33.22</v>
-      </c>
       <c r="AA5" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC5" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD5" t="n">
         <v>0.88</v>
       </c>
-      <c r="AD5" t="s">
-        <v>58</v>
-      </c>
       <c r="AE5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AF5" t="n">
+        <v>64</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG5" t="n">
         <v>0.88</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>13.11</v>
       </c>
-      <c r="AH5" t="n">
-        <v>36.55</v>
-      </c>
       <c r="AI5" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>0.22</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>1.26</v>
       </c>
-      <c r="AK5" t="s">
-        <v>60</v>
-      </c>
       <c r="AL5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="AM5" t="s">
-        <v>62</v>
+        <v>67</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D6" t="n">
-        <v>901.5</v>
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>70</v>
       </c>
       <c r="E6" t="n">
-        <v>8.92</v>
+        <v>115.45</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>-4.84</v>
       </c>
       <c r="G6" t="n">
-        <v>900</v>
+        <v>-4.02</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>115.3</v>
       </c>
       <c r="I6" t="n">
-        <v>901.4</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>115.5</v>
       </c>
       <c r="K6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" t="n">
-        <v>892.58</v>
+        <v>71</v>
+      </c>
+      <c r="L6" t="s">
+        <v>72</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>120.29</v>
       </c>
       <c r="N6" t="n">
-        <v>934.92</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>866</v>
-      </c>
-      <c r="P6" t="s">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>60.38</v>
-      </c>
-      <c r="R6" t="s">
-        <v>66</v>
+        <v>132.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>18.97</v>
       </c>
       <c r="S6" t="n">
-        <v>267.6</v>
+        <v>230.9</v>
       </c>
       <c r="T6" t="n">
-        <v>956.10633</v>
-      </c>
-      <c r="U6" t="s">
-        <v>67</v>
-      </c>
-      <c r="V6" t="s">
-        <v>68</v>
+        <v>-9.68</v>
+      </c>
+      <c r="U6" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="V6" t="n">
+        <v>239.4</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="X6" t="s">
-        <v>67</v>
+        <v>-8.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-3.55</v>
       </c>
       <c r="Y6" t="n">
-        <v>956.11</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>68</v>
+        <v>239.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>119.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>42</v>
+        <v>-8.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
       </c>
       <c r="AE6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>44</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>277.73</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>69</v>
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.19</v>
       </c>
       <c r="AL6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AM6" t="s">
-        <v>71</v>
+        <v>75</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-16.36</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="H7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="n">
-        <v>415.0953</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-5.6747</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="G7" t="n">
-        <v>415.06</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>418.95</v>
-      </c>
-      <c r="J7" t="n">
-        <v>30</v>
-      </c>
-      <c r="K7" t="s">
-        <v>73</v>
-      </c>
-      <c r="L7" t="n">
-        <v>420.77</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
+      <c r="J7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" t="n">
+        <v>46</v>
+      </c>
+      <c r="L7" t="s">
+        <v>82</v>
+      </c>
+      <c r="M7" t="s">
+        <v>83</v>
       </c>
       <c r="N7" t="n">
-        <v>418.63</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>555.45</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>356.28</v>
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>84</v>
       </c>
       <c r="R7" t="n">
-        <v>830.19</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-11.35</v>
+        <v>71.04</v>
+      </c>
+      <c r="S7" t="s">
+        <v>85</v>
       </c>
       <c r="T7" t="n">
-        <v>386.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>773</v>
-      </c>
-      <c r="V7" t="n">
-        <v>57.19</v>
+        <v>-327.2</v>
+      </c>
+      <c r="U7" t="s">
+        <v>86</v>
+      </c>
+      <c r="V7" t="s">
+        <v>87</v>
       </c>
       <c r="W7" t="n">
-        <v>7.4</v>
+        <v>-196.76</v>
       </c>
       <c r="X7" t="n">
-        <v>773</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>386.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>57.19</v>
+        <v>-0.96</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>88</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>74</v>
+        <v>-196.76</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
       </c>
       <c r="AE7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>3.64</v>
+        <v>44</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>44</v>
       </c>
       <c r="AG7" t="n">
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>25.89</v>
+        <v>3.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.87</v>
+        <v>179.13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>76</v>
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.53</v>
       </c>
       <c r="AL7" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AM7" t="s">
-        <v>78</v>
+        <v>90</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="8" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>712.105</v>
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>93</v>
       </c>
       <c r="E8" t="n">
-        <v>17.165</v>
+        <v>406.09</v>
       </c>
       <c r="F8" t="n">
-        <v>2.47</v>
+        <v>0.88</v>
       </c>
       <c r="G8" t="n">
-        <v>711</v>
+        <v>0.22</v>
       </c>
       <c r="H8" t="n">
-        <v>22</v>
+        <v>406.05</v>
       </c>
       <c r="I8" t="n">
-        <v>712.08</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>80</v>
-      </c>
-      <c r="L8" t="n">
-        <v>694.94</v>
+        <v>406.33</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>94</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>405.21</v>
       </c>
       <c r="N8" t="n">
-        <v>711.14</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>699.53</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>701.24</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>476.78</v>
+        <v>555.45</v>
       </c>
       <c r="R8" t="n">
-        <v>712.11</v>
+        <v>356.28</v>
       </c>
       <c r="S8" t="n">
-        <v>17.17</v>
+        <v>812.18</v>
       </c>
       <c r="T8" t="n">
-        <v>619.5</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>619.5</v>
+        <v>386.5</v>
       </c>
       <c r="V8" t="n">
-        <v>92.61</v>
+        <v>773</v>
       </c>
       <c r="W8" t="n">
-        <v>14.95</v>
+        <v>39.18</v>
       </c>
       <c r="X8" t="n">
-        <v>619.5</v>
+        <v>5.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>619.5</v>
+        <v>773</v>
       </c>
       <c r="Z8" t="n">
-        <v>92.61</v>
+        <v>386.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>14.95</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>82</v>
+        <v>39.18</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.64</v>
       </c>
       <c r="AE8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.82</v>
+        <v>95</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>96</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AH8" t="n">
-        <v>33.49</v>
+        <v>16.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.41</v>
+        <v>25.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>84</v>
+        <v>0.9</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.1</v>
       </c>
       <c r="AL8" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AM8" t="s">
-        <v>86</v>
+        <v>98</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="9" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="n">
+        <v>796.26</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-7.37</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="H9" t="n">
+        <v>796.22</v>
+      </c>
+      <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
-        <v>127.7</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="G9" t="n">
-        <v>127.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" t="n">
-        <v>133.5</v>
-      </c>
       <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>88</v>
-      </c>
-      <c r="L9" t="n">
-        <v>122.62</v>
+        <v>796.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11</v>
+      </c>
+      <c r="L9" t="s">
+        <v>102</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>803.63</v>
       </c>
       <c r="N9" t="n">
-        <v>127.25</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>122.63</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>137.44</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.9</v>
+        <v>818.67</v>
       </c>
       <c r="R9" t="n">
-        <v>127.7</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5.08</v>
+        <v>90.93</v>
+      </c>
+      <c r="S9" t="s">
+        <v>103</v>
       </c>
       <c r="T9" t="n">
-        <v>122.27</v>
+        <v>-36.85</v>
       </c>
       <c r="U9" t="n">
-        <v>122.27</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.43</v>
+        <v>745.372</v>
+      </c>
+      <c r="V9" t="s">
+        <v>104</v>
       </c>
       <c r="W9" t="n">
-        <v>4.44</v>
+        <v>254.44</v>
       </c>
       <c r="X9" t="n">
-        <v>122.27</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>122.27</v>
+        <v>6.83</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>104</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.43</v>
+        <v>745.37</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>42</v>
+        <v>254.44</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.6</v>
       </c>
       <c r="AE9" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>106</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>21.18</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>36.19</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>90</v>
+        <v>0.08</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.92</v>
       </c>
       <c r="AL9" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="AM9" t="s">
-        <v>92</v>
+        <v>108</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="10" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>72.78</v>
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>111</v>
       </c>
       <c r="E10" t="n">
-        <v>1.18</v>
+        <v>715.011</v>
       </c>
       <c r="F10" t="n">
-        <v>1.65</v>
+        <v>0.301</v>
       </c>
       <c r="G10" t="n">
-        <v>72.78</v>
+        <v>0.04</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>714.97</v>
       </c>
       <c r="I10" t="n">
-        <v>73.99</v>
+        <v>540</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>94</v>
-      </c>
-      <c r="L10" t="n">
-        <v>71.6</v>
+        <v>715.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>140</v>
+      </c>
+      <c r="L10" t="s">
+        <v>112</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>714.71</v>
       </c>
       <c r="N10" t="n">
-        <v>73.83</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>72.29</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>109.83</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>29.1</v>
+        <v>716.65</v>
       </c>
       <c r="R10" t="n">
-        <v>218.34</v>
+        <v>505.58</v>
       </c>
       <c r="S10" t="n">
-        <v>3.54</v>
+        <v>715.01</v>
       </c>
       <c r="T10" t="n">
-        <v>74.94667</v>
+        <v>0.3</v>
       </c>
       <c r="U10" t="n">
-        <v>224.84</v>
+        <v>619.5</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.5</v>
+        <v>619.5</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.89</v>
+        <v>95.51</v>
       </c>
       <c r="X10" t="n">
-        <v>224.84</v>
+        <v>15.42</v>
       </c>
       <c r="Y10" t="n">
-        <v>74.95</v>
+        <v>619.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>-6.5</v>
+        <v>619.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>42</v>
+        <v>95.51</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.82</v>
       </c>
       <c r="AE10" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>115</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>33.49</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>95</v>
+        <v>0.4</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.21</v>
       </c>
       <c r="AL10" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="AM10" t="s">
-        <v>97</v>
+        <v>117</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="11" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
-        <v>427.98</v>
+      <c r="D11" t="s">
+        <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>16.19</v>
+        <v>133.97</v>
       </c>
       <c r="F11" t="n">
-        <v>3.93</v>
+        <v>0.74</v>
       </c>
       <c r="G11" t="n">
-        <v>427.98</v>
+        <v>0.56</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>133.2</v>
       </c>
       <c r="I11" t="n">
-        <v>428</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K11" t="s">
-        <v>99</v>
-      </c>
-      <c r="L11" t="n">
-        <v>411.79</v>
+        <v>134</v>
+      </c>
+      <c r="K11" t="n">
+        <v>95</v>
+      </c>
+      <c r="L11" t="s">
+        <v>121</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>133.23</v>
       </c>
       <c r="N11" t="n">
-        <v>431.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>416.39</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>498.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>271</v>
+        <v>137.47</v>
       </c>
       <c r="R11" t="n">
-        <v>427.98</v>
+        <v>14.9</v>
       </c>
       <c r="S11" t="n">
-        <v>16.19</v>
+        <v>133.97</v>
       </c>
       <c r="T11" t="n">
-        <v>468.88</v>
+        <v>0.74</v>
       </c>
       <c r="U11" t="n">
-        <v>468.88</v>
+        <v>122.27</v>
       </c>
       <c r="V11" t="n">
-        <v>-40.9</v>
+        <v>122.27</v>
       </c>
       <c r="W11" t="n">
-        <v>-8.72</v>
+        <v>11.7</v>
       </c>
       <c r="X11" t="n">
-        <v>468.88</v>
+        <v>9.57</v>
       </c>
       <c r="Y11" t="n">
-        <v>468.88</v>
+        <v>122.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>-40.9</v>
+        <v>122.27</v>
       </c>
       <c r="AA11" t="n">
-        <v>-8.72</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>42</v>
+        <v>11.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
       </c>
       <c r="AE11" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>44</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>365.81</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>101</v>
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.96</v>
       </c>
       <c r="AL11" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="AM11" t="s">
-        <v>103</v>
+        <v>124</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="12" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A12" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" t="n">
+        <v>77.5949</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.7551</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="H12" t="n">
+        <v>77.58</v>
+      </c>
+      <c r="I12" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" t="n">
+        <v>77.63</v>
+      </c>
+      <c r="K12" t="n">
+        <v>300</v>
+      </c>
+      <c r="L12" t="s">
+        <v>129</v>
+      </c>
+      <c r="M12" t="n">
+        <v>79.35</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>109.83</v>
+      </c>
+      <c r="R12" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>232.78</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="U12" t="n">
+        <v>74.94667</v>
+      </c>
+      <c r="V12" t="n">
+        <v>224.84</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>224.84</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>131</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" collapsed="0" hidden="0" customHeight="0" spans="1:1">
+      <c r="A13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-40.75</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="H13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I13" t="n">
+        <v>85</v>
+      </c>
+      <c r="J13" t="s">
+        <v>136</v>
+      </c>
+      <c r="K13" t="n">
+        <v>80</v>
+      </c>
+      <c r="L13" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13" t="s">
+        <v>138</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>139</v>
+      </c>
+      <c r="R13" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="S13" t="s">
+        <v>140</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-81.5</v>
+      </c>
+      <c r="U13" t="s">
+        <v>141</v>
+      </c>
+      <c r="V13" t="s">
+        <v>142</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-57.14</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-57.14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>143</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>144</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" collapsed="0" hidden="0" customHeight="0" spans="1:1">
+      <c r="A14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
-        <v>678.425</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5.885</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G12" t="n">
-        <v>677.98</v>
-      </c>
-      <c r="H12" t="n">
-        <v>199</v>
-      </c>
-      <c r="I12" t="n">
-        <v>688</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="s">
-        <v>105</v>
-      </c>
-      <c r="L12" t="n">
-        <v>672.54</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>678.51</v>
-      </c>
-      <c r="O12" t="n">
-        <v>675.43</v>
-      </c>
-      <c r="P12" t="n">
-        <v>676.76</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>511.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>678.43</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="D14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" t="n">
+        <v>449.095</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H14" t="n">
+        <v>449.11</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>449.19</v>
+      </c>
+      <c r="K14" t="n">
+        <v>994</v>
+      </c>
+      <c r="L14" t="s">
+        <v>148</v>
+      </c>
+      <c r="M14" t="n">
+        <v>445.27</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>498.83</v>
+      </c>
+      <c r="R14" t="n">
+        <v>273.21</v>
+      </c>
+      <c r="S14" t="n">
+        <v>449.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="U14" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="V14" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-19.78</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-19.78</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>397.66</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>150</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>151</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" collapsed="0" hidden="0" customHeight="0" spans="1:1">
+      <c r="A15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" t="n">
+        <v>684.26</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H15" t="n">
+        <v>684.22</v>
+      </c>
+      <c r="I15" t="n">
+        <v>236</v>
+      </c>
+      <c r="J15" t="n">
+        <v>684.31</v>
+      </c>
+      <c r="K15" t="n">
+        <v>236</v>
+      </c>
+      <c r="L15" t="s">
+        <v>155</v>
+      </c>
+      <c r="M15" t="n">
+        <v>682.41</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>683.91</v>
+      </c>
+      <c r="R15" t="n">
+        <v>529.11</v>
+      </c>
+      <c r="S15" t="n">
+        <v>684.26</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U15" t="n">
         <v>629.5</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V15" t="n">
         <v>629.5</v>
       </c>
-      <c r="V12" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="W12" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="W15" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="X15" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="Y15" t="n">
         <v>629.5</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z15" t="n">
         <v>629.5</v>
       </c>
-      <c r="Z12" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AA15" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD15" t="n">
         <v>7.13</v>
       </c>
-      <c r="AD12" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>106</v>
-      </c>
-      <c r="AF12" t="n">
+      <c r="AE15" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG15" t="n">
         <v>7.13</v>
       </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
         <v>26.2</v>
       </c>
-      <c r="AI12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="AJ15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1</v>
       </c>
-      <c r="AK12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>109</v>
+      <c r="AL15" t="s">
+        <v>157</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/data/67744964-positions.xlsx
+++ b/data/67744964-positions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
   <si>
     <t>代號</t>
   </si>
@@ -139,208 +139,328 @@
     <t>Advanced Micro Devices Inc.</t>
   </si>
   <si>
-    <t>1,134,024</t>
+    <t>15,593,126</t>
+  </si>
+  <si>
+    <t>05/19/2026</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>41,628,729</t>
+  </si>
+  <si>
+    <t>850,423</t>
+  </si>
+  <si>
+    <t>3.66%</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>Amazon.com Inc.</t>
+  </si>
+  <si>
+    <t>21,172,124</t>
+  </si>
+  <si>
+    <t>43,918,336</t>
+  </si>
+  <si>
+    <t>2,759,414</t>
+  </si>
+  <si>
+    <t>3.43%</t>
+  </si>
+  <si>
+    <t>DXYZ</t>
+  </si>
+  <si>
+    <t>Destiny Tech100 Inc.</t>
+  </si>
+  <si>
+    <t>5,050,377</t>
+  </si>
+  <si>
+    <t>05/29/2026</t>
+  </si>
+  <si>
+    <t>5,174,004</t>
+  </si>
+  <si>
+    <t>16,944</t>
+  </si>
+  <si>
+    <t>0.28%</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>Alphabet Inc.</t>
+  </si>
+  <si>
+    <t>20,237,751</t>
+  </si>
+  <si>
+    <t>05/01/2026</t>
+  </si>
+  <si>
+    <t>06/08/2026</t>
+  </si>
+  <si>
+    <t>06/15/2026</t>
+  </si>
+  <si>
+    <t>20,057,158</t>
+  </si>
+  <si>
+    <t>4,384,175</t>
+  </si>
+  <si>
+    <t>4.87%</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>Intel Corporation</t>
+  </si>
+  <si>
+    <t>75,006,350</t>
+  </si>
+  <si>
+    <t>147,387,954</t>
+  </si>
+  <si>
+    <t>542,456</t>
+  </si>
+  <si>
+    <t>3.07%</t>
+  </si>
+  <si>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>Lumentum Holdings Inc.</t>
+  </si>
+  <si>
+    <t>3,398,701</t>
+  </si>
+  <si>
+    <t>1,029.15</t>
+  </si>
+  <si>
+    <t>1,049.53</t>
+  </si>
+  <si>
+    <t>1,085.68</t>
+  </si>
+  <si>
+    <t>1,898.94</t>
+  </si>
+  <si>
+    <t>1,857.12</t>
+  </si>
+  <si>
+    <t>2,452.23</t>
+  </si>
+  <si>
+    <t>1,226.12</t>
+  </si>
+  <si>
+    <t>05/21/2026</t>
+  </si>
+  <si>
+    <t>6,054,979</t>
+  </si>
+  <si>
+    <t>80,068</t>
+  </si>
+  <si>
+    <t>13.00%</t>
+  </si>
+  <si>
+    <t>MU</t>
+  </si>
+  <si>
+    <t>Micron Technology Inc.</t>
+  </si>
+  <si>
+    <t>1,065.335</t>
+  </si>
+  <si>
+    <t>1,065.01</t>
+  </si>
+  <si>
+    <t>1,065.67</t>
+  </si>
+  <si>
+    <t>20,773,438</t>
+  </si>
+  <si>
+    <t>1,064.10</t>
+  </si>
+  <si>
+    <t>1,088.71</t>
+  </si>
+  <si>
+    <t>1,038.50</t>
+  </si>
+  <si>
+    <t>1,076.56</t>
+  </si>
+  <si>
+    <t>2,130.67</t>
+  </si>
+  <si>
+    <t>1,024.00</t>
+  </si>
+  <si>
+    <t>2,048.00</t>
+  </si>
+  <si>
+    <t>06/01/2026</t>
+  </si>
+  <si>
+    <t>03/30/2026</t>
+  </si>
+  <si>
+    <t>04/15/2026</t>
+  </si>
+  <si>
+    <t>50,554,631</t>
+  </si>
+  <si>
+    <t>1,200,022</t>
+  </si>
+  <si>
+    <t>14.59%</t>
+  </si>
+  <si>
+    <t>MUU</t>
+  </si>
+  <si>
+    <t>Direxion Daily MU Bull 2X Shares</t>
+  </si>
+  <si>
+    <t>1,038.00</t>
+  </si>
+  <si>
+    <t>1,035.00</t>
+  </si>
+  <si>
+    <t>1,701,811</t>
+  </si>
+  <si>
+    <t>1,033.17</t>
+  </si>
+  <si>
+    <t>1,080.36</t>
+  </si>
+  <si>
+    <t>1,055.79</t>
+  </si>
+  <si>
+    <t>2,076.00</t>
+  </si>
+  <si>
+    <t>1,973.15</t>
+  </si>
+  <si>
+    <t>03/24/2026</t>
+  </si>
+  <si>
+    <t>03/31/2026</t>
+  </si>
+  <si>
+    <t>2,813,082</t>
+  </si>
+  <si>
+    <t>7,232</t>
+  </si>
+  <si>
+    <t>14.21%</t>
+  </si>
+  <si>
+    <t>NOK</t>
+  </si>
+  <si>
+    <t>Nokia Corporation Sponsored American Depositary Shares</t>
+  </si>
+  <si>
+    <t>5,012</t>
+  </si>
+  <si>
+    <t>7,970</t>
+  </si>
+  <si>
+    <t>99,956,310</t>
+  </si>
+  <si>
+    <t>05/14/2026</t>
   </si>
   <si>
     <t>04/28/2026</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>42,878,903</t>
-  </si>
-  <si>
-    <t>726,433</t>
-  </si>
-  <si>
-    <t>1.35%</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>Amazon.com Inc.</t>
-  </si>
-  <si>
-    <t>380,105</t>
-  </si>
-  <si>
-    <t>46,600,610</t>
-  </si>
-  <si>
-    <t>2,905,818</t>
-  </si>
-  <si>
-    <t>1.67%</t>
-  </si>
-  <si>
-    <t>CPER</t>
-  </si>
-  <si>
-    <t>United States Copper Index Fund</t>
-  </si>
-  <si>
-    <t>1,000</t>
-  </si>
-  <si>
-    <t>29,633</t>
-  </si>
-  <si>
-    <t>800,928</t>
-  </si>
-  <si>
-    <t>0.37%</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>Alphabet Inc.</t>
-  </si>
-  <si>
-    <t>268,768</t>
-  </si>
-  <si>
-    <t>05/01/2026</t>
-  </si>
-  <si>
-    <t>06/08/2026</t>
-  </si>
-  <si>
-    <t>06/15/2026</t>
-  </si>
-  <si>
-    <t>17,747,786</t>
-  </si>
-  <si>
-    <t>4,878,144</t>
-  </si>
-  <si>
-    <t>2.46%</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>Intel Corporation</t>
-  </si>
-  <si>
-    <t>1,344</t>
-  </si>
-  <si>
-    <t>6,254,824</t>
-  </si>
-  <si>
     <t>05/12/2026</t>
   </si>
   <si>
-    <t>144,227,256</t>
-  </si>
-  <si>
-    <t>604,578</t>
-  </si>
-  <si>
-    <t>0.72%</t>
-  </si>
-  <si>
-    <t>LITE</t>
-  </si>
-  <si>
-    <t>Lumentum Holdings Inc.</t>
-  </si>
-  <si>
-    <t>1,014.01</t>
-  </si>
-  <si>
-    <t>1,013.00</t>
-  </si>
-  <si>
-    <t>1,017.45</t>
-  </si>
-  <si>
-    <t>105,983</t>
-  </si>
-  <si>
-    <t>1,030.37</t>
-  </si>
-  <si>
-    <t>1,085.68</t>
-  </si>
-  <si>
-    <t>20,280.20</t>
-  </si>
-  <si>
-    <t>1,023.848</t>
-  </si>
-  <si>
-    <t>20,476.96</t>
-  </si>
-  <si>
-    <t>1,023.85</t>
-  </si>
-  <si>
-    <t>6,092,637</t>
-  </si>
-  <si>
-    <t>80,163</t>
-  </si>
-  <si>
-    <t>62.94%</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>Microsoft Corporation</t>
-  </si>
-  <si>
-    <t>485,646</t>
-  </si>
-  <si>
-    <t>05/21/2026</t>
-  </si>
-  <si>
-    <t>06/11/2026</t>
-  </si>
-  <si>
-    <t>33,407,786</t>
-  </si>
-  <si>
-    <t>3,010,076</t>
-  </si>
-  <si>
-    <t>2.52%</t>
-  </si>
-  <si>
-    <t>MU</t>
-  </si>
-  <si>
-    <t>Micron Technology Inc.</t>
-  </si>
-  <si>
-    <t>1,983,537</t>
-  </si>
-  <si>
-    <t>3,981.30</t>
-  </si>
-  <si>
-    <t>3,726.86</t>
-  </si>
-  <si>
-    <t>03/30/2026</t>
-  </si>
-  <si>
-    <t>04/15/2026</t>
-  </si>
-  <si>
-    <t>46,296,949</t>
-  </si>
-  <si>
-    <t>906,281</t>
-  </si>
-  <si>
-    <t>12.36%</t>
+    <t>123,435,010</t>
+  </si>
+  <si>
+    <t>96,757</t>
+  </si>
+  <si>
+    <t>2.36%</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>ServiceNow Inc.</t>
+  </si>
+  <si>
+    <t>18,671,888</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>33,434,912</t>
+  </si>
+  <si>
+    <t>131,607</t>
+  </si>
+  <si>
+    <t>0.83%</t>
+  </si>
+  <si>
+    <t>NOWL</t>
+  </si>
+  <si>
+    <t>GraniteShares 2x Long NOW Daily ETF</t>
+  </si>
+  <si>
+    <t>11,122</t>
+  </si>
+  <si>
+    <t>12,884</t>
+  </si>
+  <si>
+    <t>24,239,902</t>
+  </si>
+  <si>
+    <t>22,965,784</t>
+  </si>
+  <si>
+    <t>4,523</t>
+  </si>
+  <si>
+    <t>0.92%</t>
   </si>
   <si>
     <t>QQQ</t>
@@ -349,7 +469,7 @@
     <t>INVESCO QQQ Trust</t>
   </si>
   <si>
-    <t>1,117,521</t>
+    <t>19,955,108</t>
   </si>
   <si>
     <t>12/23/2025</t>
@@ -361,34 +481,13 @@
     <t>03/27/2026</t>
   </si>
   <si>
-    <t>42,551,499</t>
-  </si>
-  <si>
-    <t>466,777</t>
-  </si>
-  <si>
-    <t>2.22%</t>
-  </si>
-  <si>
-    <t>SATS</t>
-  </si>
-  <si>
-    <t>EchoStar Corporation</t>
-  </si>
-  <si>
-    <t>30,093</t>
-  </si>
-  <si>
-    <t>04/29/2026</t>
-  </si>
-  <si>
-    <t>5,342,680</t>
-  </si>
-  <si>
-    <t>38,612</t>
-  </si>
-  <si>
-    <t>0.42%</t>
+    <t>38,411,776</t>
+  </si>
+  <si>
+    <t>499,256</t>
+  </si>
+  <si>
+    <t>5.09%</t>
   </si>
   <si>
     <t>SLV</t>
@@ -397,16 +496,16 @@
     <t>iShares Silver Trust</t>
   </si>
   <si>
-    <t>2,800</t>
-  </si>
-  <si>
-    <t>2,583,891</t>
-  </si>
-  <si>
-    <t>24,934,175</t>
-  </si>
-  <si>
-    <t>42,416</t>
+    <t>7,991,122</t>
+  </si>
+  <si>
+    <t>21,758,328</t>
+  </si>
+  <si>
+    <t>36,514</t>
+  </si>
+  <si>
+    <t>1.36%</t>
   </si>
   <si>
     <t>SNDK</t>
@@ -415,40 +514,49 @@
     <t>Sandisk Corporation</t>
   </si>
   <si>
-    <t>1,406.48</t>
-  </si>
-  <si>
-    <t>1,405.42</t>
-  </si>
-  <si>
-    <t>1,407.19</t>
-  </si>
-  <si>
-    <t>524,453</t>
-  </si>
-  <si>
-    <t>1,447.23</t>
-  </si>
-  <si>
-    <t>1,600.00</t>
-  </si>
-  <si>
-    <t>2,812.96</t>
-  </si>
-  <si>
-    <t>1,435.05</t>
-  </si>
-  <si>
-    <t>2,870.10</t>
-  </si>
-  <si>
-    <t>16,315,380</t>
-  </si>
-  <si>
-    <t>214,320</t>
-  </si>
-  <si>
-    <t>8.73%</t>
+    <t>1,800.665</t>
+  </si>
+  <si>
+    <t>1,800.18</t>
+  </si>
+  <si>
+    <t>1,801.05</t>
+  </si>
+  <si>
+    <t>5,996,226</t>
+  </si>
+  <si>
+    <t>1,716.36</t>
+  </si>
+  <si>
+    <t>1,809.50</t>
+  </si>
+  <si>
+    <t>1,708.88</t>
+  </si>
+  <si>
+    <t>1,804.00</t>
+  </si>
+  <si>
+    <t>3,601.33</t>
+  </si>
+  <si>
+    <t>1,737.015</t>
+  </si>
+  <si>
+    <t>3,474.03</t>
+  </si>
+  <si>
+    <t>1,737.02</t>
+  </si>
+  <si>
+    <t>13,726,077</t>
+  </si>
+  <si>
+    <t>254,175</t>
+  </si>
+  <si>
+    <t>24.66%</t>
   </si>
   <si>
     <t>TSLA</t>
@@ -457,19 +565,19 @@
     <t>Tesla Inc.</t>
   </si>
   <si>
-    <t>1,579,745</t>
+    <t>24,948,645</t>
   </si>
   <si>
     <t>12/29/2025</t>
   </si>
   <si>
-    <t>65,549,500</t>
-  </si>
-  <si>
-    <t>1,672,311</t>
-  </si>
-  <si>
-    <t>1.39%</t>
+    <t>53,903,795</t>
+  </si>
+  <si>
+    <t>1,591,450</t>
+  </si>
+  <si>
+    <t>2.90%</t>
   </si>
   <si>
     <t>VOO</t>
@@ -478,19 +586,16 @@
     <t>Vanguard S&amp;P 500 ETF</t>
   </si>
   <si>
-    <t>94,275</t>
-  </si>
-  <si>
-    <t>03/31/2026</t>
-  </si>
-  <si>
-    <t>6,336,641</t>
-  </si>
-  <si>
-    <t>933,607</t>
-  </si>
-  <si>
-    <t>2.12%</t>
+    <t>2,684,606</t>
+  </si>
+  <si>
+    <t>6,073,371</t>
+  </si>
+  <si>
+    <t>931,703</t>
+  </si>
+  <si>
+    <t>4.75%</t>
   </si>
 </sst>
 </file>
@@ -1014,76 +1119,76 @@
         <v>41</v>
       </c>
       <c r="E2" t="n">
-        <v>435.9536</v>
+        <v>534.1872</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.5464</v>
+        <v>12.6472</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.14</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="n">
-        <v>435.7</v>
+        <v>534.22</v>
       </c>
       <c r="I2" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>435.99</v>
+        <v>534.55</v>
       </c>
       <c r="K2" t="n">
-        <v>120</v>
+        <v>242</v>
       </c>
       <c r="L2" t="s">
         <v>42</v>
       </c>
       <c r="M2" t="n">
-        <v>445.5</v>
+        <v>521.54</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>544.04</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>524.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>469.22</v>
+        <v>527.2</v>
       </c>
       <c r="R2" t="n">
-        <v>107.67</v>
+        <v>111.01</v>
       </c>
       <c r="S2" t="n">
-        <v>435.95</v>
+        <v>534.19</v>
       </c>
       <c r="T2" t="n">
-        <v>-9.55</v>
+        <v>12.65</v>
       </c>
       <c r="U2" t="n">
-        <v>322.7</v>
+        <v>415.71</v>
       </c>
       <c r="V2" t="n">
-        <v>322.7</v>
+        <v>415.71</v>
       </c>
       <c r="W2" t="n">
-        <v>113.25</v>
+        <v>118.48</v>
       </c>
       <c r="X2" t="n">
-        <v>35.1</v>
+        <v>28.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>322.7</v>
+        <v>415.71</v>
       </c>
       <c r="Z2" t="n">
-        <v>322.7</v>
+        <v>415.71</v>
       </c>
       <c r="AA2" t="n">
-        <v>113.25</v>
+        <v>118.48</v>
       </c>
       <c r="AB2" t="n">
-        <v>35.1</v>
+        <v>28.5</v>
       </c>
       <c r="AC2" t="s">
         <v>43</v>
@@ -1104,13 +1209,13 @@
         <v>3.05</v>
       </c>
       <c r="AI2" t="n">
-        <v>146.98</v>
+        <v>167.26</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL2" t="s">
         <v>45</v>
@@ -1133,40 +1238,40 @@
         <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>269</v>
+        <v>250.17</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.13</v>
+        <v>-6.35</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.42</v>
+        <v>-2.48</v>
       </c>
       <c r="H3" t="n">
-        <v>269</v>
+        <v>250.14</v>
       </c>
       <c r="I3" t="n">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>269.12</v>
+        <v>250.16</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>270.13</v>
+        <v>256.52</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>257.09</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>249.11</v>
       </c>
       <c r="Q3" t="n">
         <v>278.56</v>
@@ -1175,10 +1280,10 @@
         <v>196</v>
       </c>
       <c r="S3" t="n">
-        <v>538</v>
+        <v>500.34</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.26</v>
+        <v>-12.7</v>
       </c>
       <c r="U3" t="n">
         <v>236.55</v>
@@ -1187,10 +1292,10 @@
         <v>473.1</v>
       </c>
       <c r="W3" t="n">
-        <v>64.9</v>
+        <v>27.24</v>
       </c>
       <c r="X3" t="n">
-        <v>13.72</v>
+        <v>5.76</v>
       </c>
       <c r="Y3" t="n">
         <v>473.1</v>
@@ -1199,10 +1304,10 @@
         <v>236.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>64.9</v>
+        <v>27.24</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.72</v>
+        <v>5.76</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1220,13 +1325,13 @@
         <v>8.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>37.07</v>
+        <v>36.44</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL3" t="s">
         <v>51</v>
@@ -1243,82 +1348,85 @@
         <v>54</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>55</v>
       </c>
       <c r="E4" t="n">
-        <v>40.19</v>
+        <v>41.43</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08</v>
+        <v>-5.8</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2</v>
+        <v>-12.28</v>
       </c>
       <c r="H4" t="n">
-        <v>40.11</v>
+        <v>41.4</v>
       </c>
       <c r="I4" t="n">
-        <v>800</v>
+        <v>202</v>
       </c>
       <c r="J4" t="n">
-        <v>40.26</v>
-      </c>
-      <c r="K4" t="s">
+        <v>41.48</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" t="s">
         <v>56</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="P4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="R4" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="S4" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-16.64</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-16.64</v>
+      </c>
+      <c r="AC4" t="s">
         <v>57</v>
-      </c>
-      <c r="M4" t="n">
-        <v>40.27</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="R4" t="n">
-        <v>27.08</v>
-      </c>
-      <c r="S4" t="n">
-        <v>120.57</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="U4" t="n">
-        <v>36.69</v>
-      </c>
-      <c r="V4" t="n">
-        <v>110.07</v>
-      </c>
-      <c r="W4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>9.54</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>110.07</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>36.69</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.54</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1336,81 +1444,81 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>24.42</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.46</v>
+        <v>5.11</v>
       </c>
       <c r="AL4" t="s">
         <v>58</v>
       </c>
-      <c r="AM4" t="n">
-        <v>775</v>
+      <c r="AM4" t="s">
+        <v>59</v>
       </c>
       <c r="AN4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E5" t="n">
-        <v>396.37</v>
+        <v>355.84</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.67</v>
+        <v>-2.55</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.67</v>
+        <v>-0.71</v>
       </c>
       <c r="H5" t="n">
-        <v>396.29</v>
+        <v>355.85</v>
       </c>
       <c r="I5" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="J5" t="n">
-        <v>396.46</v>
+        <v>355.88</v>
       </c>
       <c r="K5" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M5" t="n">
-        <v>399.04</v>
+        <v>358.39</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>354.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>399.93</v>
+        <v>404.47</v>
       </c>
       <c r="R5" t="n">
-        <v>157.58</v>
+        <v>163.33</v>
       </c>
       <c r="S5" t="n">
-        <v>792.74</v>
+        <v>711.68</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.34</v>
+        <v>-5.1</v>
       </c>
       <c r="U5" t="n">
         <v>379.19</v>
@@ -1419,10 +1527,10 @@
         <v>758.38</v>
       </c>
       <c r="W5" t="n">
-        <v>34.36</v>
+        <v>-46.7</v>
       </c>
       <c r="X5" t="n">
-        <v>4.53</v>
+        <v>-6.16</v>
       </c>
       <c r="Y5" t="n">
         <v>758.38</v>
@@ -1431,22 +1539,22 @@
         <v>379.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>34.36</v>
+        <v>-46.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.53</v>
+        <v>-6.16</v>
       </c>
       <c r="AC5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD5" t="n">
         <v>0.88</v>
       </c>
       <c r="AE5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG5" t="n">
         <v>0.88</v>
@@ -1455,69 +1563,69 @@
         <v>13.11</v>
       </c>
       <c r="AI5" t="n">
-        <v>35.51</v>
+        <v>34.47</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AL5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AN5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" t="n">
-        <v>115.45</v>
+        <v>112.28</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.84</v>
+        <v>4.35</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.02</v>
+        <v>4.03</v>
       </c>
       <c r="H6" t="n">
-        <v>115.3</v>
+        <v>112.28</v>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="J6" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="K6" t="s">
-        <v>71</v>
+        <v>112.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>47</v>
       </c>
       <c r="L6" t="s">
         <v>72</v>
       </c>
       <c r="M6" t="n">
-        <v>120.29</v>
+        <v>107.93</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>118.29</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>111.53</v>
       </c>
       <c r="Q6" t="n">
         <v>132.75</v>
@@ -1526,37 +1634,34 @@
         <v>18.97</v>
       </c>
       <c r="S6" t="n">
-        <v>230.9</v>
+        <v>449.12</v>
       </c>
       <c r="T6" t="n">
-        <v>-9.68</v>
+        <v>17.4</v>
       </c>
       <c r="U6" t="n">
-        <v>119.7</v>
+        <v>113.705</v>
       </c>
       <c r="V6" t="n">
-        <v>239.4</v>
+        <v>454.82</v>
       </c>
       <c r="W6" t="n">
-        <v>-8.5</v>
+        <v>-5.7</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.55</v>
+        <v>-1.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>239.4</v>
+        <v>454.82</v>
       </c>
       <c r="Z6" t="n">
-        <v>119.7</v>
+        <v>113.71</v>
       </c>
       <c r="AA6" t="n">
-        <v>-8.5</v>
+        <v>-5.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>73</v>
+        <v>-1.25</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1580,99 +1685,102 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AL6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM6" t="s">
         <v>74</v>
       </c>
-      <c r="AM6" t="s">
+      <c r="AN6" t="s">
         <v>75</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="7" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
         <v>77</v>
       </c>
-      <c r="B7" t="n">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="n">
+        <v>949.47</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-79.68</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="H7" t="n">
+        <v>949.47</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>949.88</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
         <v>78</v>
       </c>
-      <c r="E7" t="s">
+      <c r="M7" t="s">
         <v>79</v>
       </c>
-      <c r="F7" t="n">
-        <v>-16.36</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
         <v>80</v>
       </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="P7" t="n">
+        <v>944.05</v>
+      </c>
+      <c r="Q7" t="s">
         <v>81</v>
       </c>
-      <c r="K7" t="n">
-        <v>46</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="R7" t="n">
+        <v>72.29</v>
+      </c>
+      <c r="S7" t="s">
         <v>82</v>
       </c>
-      <c r="M7" t="s">
+      <c r="T7" t="n">
+        <v>-159.36</v>
+      </c>
+      <c r="U7" t="n">
+        <v>928.56</v>
+      </c>
+      <c r="V7" t="s">
         <v>83</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="W7" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y7" t="s">
         <v>84</v>
       </c>
-      <c r="R7" t="n">
-        <v>71.04</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="Z7" t="s">
         <v>85</v>
       </c>
-      <c r="T7" t="n">
-        <v>-327.2</v>
-      </c>
-      <c r="U7" t="s">
+      <c r="AA7" t="n">
+        <v>-553.29</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-22.56</v>
+      </c>
+      <c r="AC7" t="s">
         <v>86</v>
-      </c>
-      <c r="V7" t="s">
-        <v>87</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-196.76</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-196.76</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.96</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1687,462 +1795,465 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.4</v>
+        <v>5.54</v>
       </c>
       <c r="AI7" t="n">
-        <v>179.13</v>
+        <v>163.36</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN7" t="s">
         <v>89</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="8" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H8" t="s">
         <v>93</v>
       </c>
-      <c r="E8" t="n">
-        <v>406.09</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H8" t="n">
-        <v>406.05</v>
-      </c>
       <c r="I8" t="n">
+        <v>16</v>
+      </c>
+      <c r="J8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" t="s">
+        <v>95</v>
+      </c>
+      <c r="M8" t="s">
+        <v>96</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>97</v>
+      </c>
+      <c r="P8" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>99</v>
+      </c>
+      <c r="R8" t="n">
+        <v>94.4</v>
+      </c>
+      <c r="S8" t="s">
         <v>100</v>
       </c>
-      <c r="J8" t="n">
-        <v>406.33</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="s">
-        <v>94</v>
-      </c>
-      <c r="M8" t="n">
-        <v>405.21</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>555.45</v>
-      </c>
-      <c r="R8" t="n">
-        <v>356.28</v>
-      </c>
-      <c r="S8" t="n">
-        <v>812.18</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U8" t="n">
-        <v>386.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>773</v>
+        <v>2.47</v>
+      </c>
+      <c r="U8" t="s">
+        <v>101</v>
+      </c>
+      <c r="V8" t="s">
+        <v>102</v>
       </c>
       <c r="W8" t="n">
-        <v>39.18</v>
+        <v>82.67</v>
       </c>
       <c r="X8" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>773</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>386.5</v>
+        <v>4.04</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>101</v>
       </c>
       <c r="AA8" t="n">
-        <v>39.18</v>
+        <v>82.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.07</v>
+        <v>4.04</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>103</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.64</v>
+        <v>0.6</v>
       </c>
       <c r="AE8" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="AF8" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.64</v>
+        <v>0.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.8</v>
+        <v>21.18</v>
       </c>
       <c r="AI8" t="n">
-        <v>25.5</v>
+        <v>48.89</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.9</v>
+        <v>0.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.1</v>
+        <v>2.17</v>
       </c>
       <c r="AL8" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AM8" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="AN8" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" t="n">
-        <v>796.26</v>
+        <v>110</v>
+      </c>
+      <c r="E9" t="s">
+        <v>111</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.37</v>
+        <v>4.83</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="H9" t="n">
-        <v>796.22</v>
+        <v>0.47</v>
+      </c>
+      <c r="H9" t="s">
+        <v>112</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>796.4</v>
+        <v>240</v>
+      </c>
+      <c r="J9" t="s">
+        <v>111</v>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L9" t="s">
-        <v>102</v>
-      </c>
-      <c r="M9" t="n">
-        <v>803.63</v>
+        <v>113</v>
+      </c>
+      <c r="M9" t="s">
+        <v>114</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
+      <c r="O9" t="s">
+        <v>115</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>818.67</v>
+        <v>985</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>116</v>
       </c>
       <c r="R9" t="n">
-        <v>90.93</v>
+        <v>14.6</v>
       </c>
       <c r="S9" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="T9" t="n">
-        <v>-36.85</v>
+        <v>40.21</v>
       </c>
       <c r="U9" t="n">
-        <v>745.372</v>
+        <v>986.575</v>
       </c>
       <c r="V9" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="W9" t="n">
-        <v>254.44</v>
+        <v>102.85</v>
       </c>
       <c r="X9" t="n">
-        <v>6.83</v>
+        <v>5.21</v>
       </c>
       <c r="Y9" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="Z9" t="n">
-        <v>745.37</v>
+        <v>986.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>254.44</v>
+        <v>102.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.83</v>
+        <v>5.21</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6</v>
+        <v>3.32</v>
       </c>
       <c r="AE9" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="AF9" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.6</v>
+        <v>3.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>21.18</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>36.19</v>
+        <v>19.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.92</v>
+        <v>10.56</v>
       </c>
       <c r="AL9" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="AM9" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="AN9" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E10" t="n">
-        <v>715.011</v>
+        <v>17.255</v>
       </c>
       <c r="F10" t="n">
-        <v>0.301</v>
+        <v>0.405</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>714.97</v>
-      </c>
-      <c r="I10" t="n">
-        <v>540</v>
+        <v>17.25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>126</v>
       </c>
       <c r="J10" t="n">
-        <v>715.05</v>
-      </c>
-      <c r="K10" t="n">
-        <v>140</v>
+        <v>17.26</v>
+      </c>
+      <c r="K10" t="s">
+        <v>127</v>
       </c>
       <c r="L10" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="M10" t="n">
-        <v>714.71</v>
+        <v>16.85</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>17.45</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>16.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>716.65</v>
+        <v>17.11</v>
       </c>
       <c r="R10" t="n">
-        <v>505.58</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>715.01</v>
+        <v>345.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3</v>
+        <v>8.1</v>
       </c>
       <c r="U10" t="n">
-        <v>619.5</v>
+        <v>14.75</v>
       </c>
       <c r="V10" t="n">
-        <v>619.5</v>
+        <v>295</v>
       </c>
       <c r="W10" t="n">
-        <v>95.51</v>
+        <v>50.1</v>
       </c>
       <c r="X10" t="n">
-        <v>15.42</v>
+        <v>16.98</v>
       </c>
       <c r="Y10" t="n">
-        <v>619.5</v>
+        <v>295</v>
       </c>
       <c r="Z10" t="n">
-        <v>619.5</v>
+        <v>14.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>95.51</v>
+        <v>50.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.42</v>
+        <v>16.98</v>
       </c>
       <c r="AC10" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.82</v>
+        <v>0.19</v>
       </c>
       <c r="AE10" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="AF10" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.82</v>
+        <v>0.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AI10" t="n">
-        <v>33.49</v>
+        <v>114.96</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.4</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AL10" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="AM10" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="AN10" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="E11" t="n">
-        <v>133.97</v>
+        <v>120.66</v>
       </c>
       <c r="F11" t="n">
-        <v>0.74</v>
+        <v>-6.99</v>
       </c>
       <c r="G11" t="n">
-        <v>0.56</v>
+        <v>-5.48</v>
       </c>
       <c r="H11" t="n">
-        <v>133.2</v>
+        <v>120.62</v>
       </c>
       <c r="I11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J11" t="n">
-        <v>134</v>
+        <v>120.68</v>
       </c>
       <c r="K11" t="n">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="M11" t="n">
-        <v>133.23</v>
+        <v>127.65</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>128.08</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>119.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>137.47</v>
+        <v>211.48</v>
       </c>
       <c r="R11" t="n">
-        <v>14.9</v>
+        <v>81.24</v>
       </c>
       <c r="S11" t="n">
-        <v>133.97</v>
+        <v>120.66</v>
       </c>
       <c r="T11" t="n">
-        <v>0.74</v>
+        <v>-6.99</v>
       </c>
       <c r="U11" t="n">
-        <v>122.27</v>
+        <v>125.09</v>
       </c>
       <c r="V11" t="n">
-        <v>122.27</v>
+        <v>125.09</v>
       </c>
       <c r="W11" t="n">
-        <v>11.7</v>
+        <v>-4.43</v>
       </c>
       <c r="X11" t="n">
-        <v>9.57</v>
+        <v>-3.54</v>
       </c>
       <c r="Y11" t="n">
-        <v>122.27</v>
+        <v>125.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>122.27</v>
+        <v>125.09</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.7</v>
+        <v>-4.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.57</v>
+        <v>-3.54</v>
       </c>
       <c r="AC11" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2157,108 +2268,111 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>81.26</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="AL11" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="AM11" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="E12" t="n">
-        <v>77.5949</v>
+        <v>6.75</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7551</v>
+        <v>-0.82</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.21</v>
+        <v>-10.83</v>
       </c>
       <c r="H12" t="n">
-        <v>77.58</v>
+        <v>6.74</v>
       </c>
       <c r="I12" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="J12" t="n">
-        <v>77.63</v>
-      </c>
-      <c r="K12" t="n">
-        <v>300</v>
+        <v>6.75</v>
+      </c>
+      <c r="K12" t="s">
+        <v>145</v>
       </c>
       <c r="L12" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="M12" t="n">
-        <v>79.35</v>
+        <v>7.57</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>109.83</v>
+        <v>29.01</v>
       </c>
       <c r="R12" t="n">
-        <v>29.1</v>
+        <v>3.49</v>
       </c>
       <c r="S12" t="n">
-        <v>232.78</v>
+        <v>135</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.27</v>
+        <v>-16.4</v>
       </c>
       <c r="U12" t="n">
-        <v>74.94667</v>
+        <v>7.34</v>
       </c>
       <c r="V12" t="n">
-        <v>224.84</v>
+        <v>146.8</v>
       </c>
       <c r="W12" t="n">
-        <v>7.94</v>
+        <v>-11.8</v>
       </c>
       <c r="X12" t="n">
-        <v>3.53</v>
+        <v>-8.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>224.84</v>
+        <v>146.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>74.95</v>
+        <v>7.34</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.94</v>
+        <v>-11.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.53</v>
+        <v>-8.04</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>138</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2276,224 +2390,224 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.45</v>
+        <v>1.28</v>
       </c>
       <c r="AL12" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="AM12" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="AN12" t="s">
-        <v>76</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" t="s">
-        <v>134</v>
+        <v>151</v>
+      </c>
+      <c r="E13" t="n">
+        <v>743.9578</v>
       </c>
       <c r="F13" t="n">
-        <v>-40.75</v>
+        <v>-2.2021</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.82</v>
-      </c>
-      <c r="H13" t="s">
-        <v>135</v>
+        <v>-0.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>743.95</v>
       </c>
       <c r="I13" t="n">
-        <v>85</v>
-      </c>
-      <c r="J13" t="s">
-        <v>136</v>
+        <v>75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>743.97</v>
       </c>
       <c r="K13" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="L13" t="s">
-        <v>137</v>
-      </c>
-      <c r="M13" t="s">
-        <v>138</v>
+        <v>152</v>
+      </c>
+      <c r="M13" t="n">
+        <v>746.16</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>748.63</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>139</v>
+        <v>741.02</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>746.44</v>
       </c>
       <c r="R13" t="n">
-        <v>35.79</v>
-      </c>
-      <c r="S13" t="s">
-        <v>140</v>
+        <v>515.97</v>
+      </c>
+      <c r="S13" t="n">
+        <v>743.96</v>
       </c>
       <c r="T13" t="n">
-        <v>-81.5</v>
-      </c>
-      <c r="U13" t="s">
-        <v>141</v>
-      </c>
-      <c r="V13" t="s">
-        <v>142</v>
+        <v>-2.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>619.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>619.5</v>
       </c>
       <c r="W13" t="n">
-        <v>-57.14</v>
+        <v>124.46</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>141</v>
+        <v>20.09</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>619.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>619.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>-57.14</v>
+        <v>124.46</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.99</v>
+        <v>20.09</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>153</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE13" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="AF13" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>32.42</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AK13" t="n">
-        <v>4.82</v>
+        <v>1.23</v>
       </c>
       <c r="AL13" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="AM13" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="AN13" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="E14" t="n">
-        <v>449.095</v>
+        <v>66.385</v>
       </c>
       <c r="F14" t="n">
-        <v>3.825</v>
+        <v>-1.605</v>
       </c>
       <c r="G14" t="n">
-        <v>0.86</v>
+        <v>-2.36</v>
       </c>
       <c r="H14" t="n">
-        <v>449.11</v>
+        <v>66.37</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="J14" t="n">
-        <v>449.19</v>
+        <v>66.39</v>
       </c>
       <c r="K14" t="n">
-        <v>994</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="M14" t="n">
-        <v>445.27</v>
+        <v>67.99</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>67.14</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>66.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>498.83</v>
+        <v>109.83</v>
       </c>
       <c r="R14" t="n">
-        <v>273.21</v>
+        <v>30.72</v>
       </c>
       <c r="S14" t="n">
-        <v>449.1</v>
+        <v>199.16</v>
       </c>
       <c r="T14" t="n">
-        <v>3.83</v>
+        <v>-4.81</v>
       </c>
       <c r="U14" t="n">
-        <v>468.88</v>
+        <v>74.94667</v>
       </c>
       <c r="V14" t="n">
-        <v>468.88</v>
+        <v>224.84</v>
       </c>
       <c r="W14" t="n">
-        <v>-19.78</v>
+        <v>-25.68</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.22</v>
+        <v>-11.42</v>
       </c>
       <c r="Y14" t="n">
-        <v>468.88</v>
+        <v>224.84</v>
       </c>
       <c r="Z14" t="n">
-        <v>468.88</v>
+        <v>74.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>-19.78</v>
+        <v>-25.68</v>
       </c>
       <c r="AB14" t="n">
-        <v>-4.22</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>149</v>
+        <v>-11.42</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2508,144 +2622,379 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>397.66</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.79</v>
+        <v>0.45</v>
       </c>
       <c r="AL14" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AM14" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="AN14" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>84.3051</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H15" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15" t="n">
+        <v>52</v>
+      </c>
+      <c r="J15" t="s">
+        <v>169</v>
+      </c>
+      <c r="K15" t="n">
+        <v>30</v>
+      </c>
+      <c r="L15" t="s">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s">
+        <v>171</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>172</v>
+      </c>
+      <c r="P15" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>174</v>
+      </c>
+      <c r="R15" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="S15" t="s">
+        <v>175</v>
+      </c>
+      <c r="T15" t="n">
+        <v>168.61</v>
+      </c>
+      <c r="U15" t="s">
+        <v>176</v>
+      </c>
+      <c r="V15" t="s">
+        <v>177</v>
+      </c>
+      <c r="W15" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>179</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>180</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" collapsed="0" hidden="0" customHeight="0" spans="1:1">
+      <c r="A16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" t="n">
+        <v>424.14</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H16" t="n">
+        <v>424.11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>101</v>
+      </c>
+      <c r="J16" t="n">
+        <v>424.17</v>
+      </c>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
+      <c r="L16" t="s">
+        <v>184</v>
+      </c>
+      <c r="M16" t="n">
+        <v>423.74</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>433.6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>416</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>498.83</v>
+      </c>
+      <c r="R16" t="n">
+        <v>273.21</v>
+      </c>
+      <c r="S16" t="n">
+        <v>424.14</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="V16" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-44.74</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-9.54</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-44.74</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-9.54</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>185</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>186</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>187</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" collapsed="0" hidden="0" customHeight="0" spans="1:1">
+      <c r="A17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>190</v>
+      </c>
+      <c r="E17" t="n">
+        <v>694.48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="H17" t="n">
+        <v>694.47</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>694.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41</v>
+      </c>
+      <c r="L17" t="s">
+        <v>191</v>
+      </c>
+      <c r="M17" t="n">
+        <v>698.26</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>697.65</v>
+      </c>
+      <c r="P17" t="n">
+        <v>693.95</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>699.15</v>
+      </c>
+      <c r="R17" t="n">
+        <v>537.8</v>
+      </c>
+      <c r="S17" t="n">
+        <v>694.48</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="U17" t="n">
+        <v>629.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>629.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="X17" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>629.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>629.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="AC17" t="s">
         <v>153</v>
       </c>
-      <c r="B15" t="n">
+      <c r="AD17" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" t="n">
-        <v>684.26</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H15" t="n">
-        <v>684.22</v>
-      </c>
-      <c r="I15" t="n">
-        <v>236</v>
-      </c>
-      <c r="J15" t="n">
-        <v>684.31</v>
-      </c>
-      <c r="K15" t="n">
-        <v>236</v>
-      </c>
-      <c r="L15" t="s">
-        <v>155</v>
-      </c>
-      <c r="M15" t="n">
-        <v>682.41</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>683.91</v>
-      </c>
-      <c r="R15" t="n">
-        <v>529.11</v>
-      </c>
-      <c r="S15" t="n">
-        <v>684.26</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U15" t="n">
-        <v>629.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>629.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="X15" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>629.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>629.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>115</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>156</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>157</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>158</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>159</v>
+      <c r="AL17" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>193</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/data/67744964-positions.xlsx
+++ b/data/67744964-positions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <si>
     <t>代號</t>
   </si>
@@ -139,7 +139,7 @@
     <t>Advanced Micro Devices Inc.</t>
   </si>
   <si>
-    <t>15,593,126</t>
+    <t>31,674,258</t>
   </si>
   <si>
     <t>05/19/2026</t>
@@ -148,13 +148,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>41,628,729</t>
-  </si>
-  <si>
-    <t>850,423</t>
-  </si>
-  <si>
-    <t>3.66%</t>
+    <t>37,397,056</t>
+  </si>
+  <si>
+    <t>796,467</t>
+  </si>
+  <si>
+    <t>3.80%</t>
   </si>
   <si>
     <t>AMZN</t>
@@ -163,16 +163,85 @@
     <t>Amazon.com Inc.</t>
   </si>
   <si>
-    <t>21,172,124</t>
-  </si>
-  <si>
-    <t>43,918,336</t>
-  </si>
-  <si>
-    <t>2,759,414</t>
-  </si>
-  <si>
-    <t>3.43%</t>
+    <t>51,323,825</t>
+  </si>
+  <si>
+    <t>42,897,561</t>
+  </si>
+  <si>
+    <t>2,597,949</t>
+  </si>
+  <si>
+    <t>3.52%</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>Broadcom Inc.</t>
+  </si>
+  <si>
+    <t>1,250</t>
+  </si>
+  <si>
+    <t>27,665,686</t>
+  </si>
+  <si>
+    <t>06/10/2026</t>
+  </si>
+  <si>
+    <t>06/22/2026</t>
+  </si>
+  <si>
+    <t>06/30/2026</t>
+  </si>
+  <si>
+    <t>27,014,158</t>
+  </si>
+  <si>
+    <t>1,834,380</t>
+  </si>
+  <si>
+    <t>2.83%</t>
+  </si>
+  <si>
+    <t>COHR</t>
+  </si>
+  <si>
+    <t>Coherent Corp.</t>
+  </si>
+  <si>
+    <t>5,391,187</t>
+  </si>
+  <si>
+    <t>06/11/2026</t>
+  </si>
+  <si>
+    <t>6,484,562</t>
+  </si>
+  <si>
+    <t>71,131</t>
+  </si>
+  <si>
+    <t>2.85%</t>
+  </si>
+  <si>
+    <t>DRAM</t>
+  </si>
+  <si>
+    <t>Roundhill Memory</t>
+  </si>
+  <si>
+    <t>32,329,721</t>
+  </si>
+  <si>
+    <t>39,891,679</t>
+  </si>
+  <si>
+    <t>16,822</t>
+  </si>
+  <si>
+    <t>2.42%</t>
   </si>
   <si>
     <t>DXYZ</t>
@@ -181,19 +250,19 @@
     <t>Destiny Tech100 Inc.</t>
   </si>
   <si>
-    <t>5,050,377</t>
+    <t>16,532,085</t>
   </si>
   <si>
     <t>05/29/2026</t>
   </si>
   <si>
-    <t>5,174,004</t>
-  </si>
-  <si>
-    <t>16,944</t>
-  </si>
-  <si>
-    <t>0.28%</t>
+    <t>6,308,942</t>
+  </si>
+  <si>
+    <t>14,706</t>
+  </si>
+  <si>
+    <t>0.22%</t>
   </si>
   <si>
     <t>GOOG</t>
@@ -202,7 +271,7 @@
     <t>Alphabet Inc.</t>
   </si>
   <si>
-    <t>20,237,751</t>
+    <t>17,681,300</t>
   </si>
   <si>
     <t>05/01/2026</t>
@@ -214,31 +283,13 @@
     <t>06/15/2026</t>
   </si>
   <si>
-    <t>20,057,158</t>
-  </si>
-  <si>
-    <t>4,384,175</t>
-  </si>
-  <si>
-    <t>4.87%</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>Intel Corporation</t>
-  </si>
-  <si>
-    <t>75,006,350</t>
-  </si>
-  <si>
-    <t>147,387,954</t>
-  </si>
-  <si>
-    <t>542,456</t>
-  </si>
-  <si>
-    <t>3.07%</t>
+    <t>22,570,713</t>
+  </si>
+  <si>
+    <t>4,334,741</t>
+  </si>
+  <si>
+    <t>5.30%</t>
   </si>
   <si>
     <t>LITE</t>
@@ -247,40 +298,55 @@
     <t>Lumentum Holdings Inc.</t>
   </si>
   <si>
-    <t>3,398,701</t>
-  </si>
-  <si>
-    <t>1,029.15</t>
-  </si>
-  <si>
-    <t>1,049.53</t>
+    <t>4,571,224</t>
   </si>
   <si>
     <t>1,085.68</t>
   </si>
   <si>
-    <t>1,898.94</t>
-  </si>
-  <si>
-    <t>1,857.12</t>
-  </si>
-  <si>
-    <t>2,452.23</t>
-  </si>
-  <si>
-    <t>1,226.12</t>
-  </si>
-  <si>
-    <t>05/21/2026</t>
-  </si>
-  <si>
-    <t>6,054,979</t>
-  </si>
-  <si>
-    <t>80,068</t>
-  </si>
-  <si>
-    <t>13.00%</t>
+    <t>1,842.00</t>
+  </si>
+  <si>
+    <t>1,749.26</t>
+  </si>
+  <si>
+    <t>2,316.08</t>
+  </si>
+  <si>
+    <t>1,158.04</t>
+  </si>
+  <si>
+    <t>6,323,631</t>
+  </si>
+  <si>
+    <t>69,210</t>
+  </si>
+  <si>
+    <t>13.60%</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>Marvell Technology Inc.</t>
+  </si>
+  <si>
+    <t>42,185,699</t>
+  </si>
+  <si>
+    <t>04/10/2026</t>
+  </si>
+  <si>
+    <t>04/30/2026</t>
+  </si>
+  <si>
+    <t>43,571,811</t>
+  </si>
+  <si>
+    <t>245,565</t>
+  </si>
+  <si>
+    <t>2.08%</t>
   </si>
   <si>
     <t>MU</t>
@@ -289,40 +355,25 @@
     <t>Micron Technology Inc.</t>
   </si>
   <si>
-    <t>1,065.335</t>
-  </si>
-  <si>
-    <t>1,065.01</t>
-  </si>
-  <si>
-    <t>1,065.67</t>
-  </si>
-  <si>
-    <t>20,773,438</t>
-  </si>
-  <si>
-    <t>1,064.10</t>
-  </si>
-  <si>
-    <t>1,088.71</t>
-  </si>
-  <si>
-    <t>1,038.50</t>
-  </si>
-  <si>
-    <t>1,076.56</t>
-  </si>
-  <si>
-    <t>2,130.67</t>
-  </si>
-  <si>
-    <t>1,024.00</t>
-  </si>
-  <si>
-    <t>2,048.00</t>
-  </si>
-  <si>
-    <t>06/01/2026</t>
+    <t>41,085,617</t>
+  </si>
+  <si>
+    <t>1,012.62</t>
+  </si>
+  <si>
+    <t>1,089.29</t>
+  </si>
+  <si>
+    <t>4,948.00</t>
+  </si>
+  <si>
+    <t>4,852.36</t>
+  </si>
+  <si>
+    <t>5,876.36</t>
+  </si>
+  <si>
+    <t>1,175.27</t>
   </si>
   <si>
     <t>03/30/2026</t>
@@ -331,13 +382,13 @@
     <t>04/15/2026</t>
   </si>
   <si>
-    <t>50,554,631</t>
-  </si>
-  <si>
-    <t>1,200,022</t>
-  </si>
-  <si>
-    <t>14.59%</t>
+    <t>55,392,828</t>
+  </si>
+  <si>
+    <t>1,123,077</t>
+  </si>
+  <si>
+    <t>36.54%</t>
   </si>
   <si>
     <t>MUU</t>
@@ -346,28 +397,10 @@
     <t>Direxion Daily MU Bull 2X Shares</t>
   </si>
   <si>
-    <t>1,038.00</t>
-  </si>
-  <si>
-    <t>1,035.00</t>
-  </si>
-  <si>
-    <t>1,701,811</t>
-  </si>
-  <si>
-    <t>1,033.17</t>
-  </si>
-  <si>
-    <t>1,080.36</t>
-  </si>
-  <si>
-    <t>1,055.79</t>
-  </si>
-  <si>
-    <t>2,076.00</t>
-  </si>
-  <si>
-    <t>1,973.15</t>
+    <t>2,876,627</t>
+  </si>
+  <si>
+    <t>1,081.71</t>
   </si>
   <si>
     <t>03/24/2026</t>
@@ -376,13 +409,13 @@
     <t>03/31/2026</t>
   </si>
   <si>
-    <t>2,813,082</t>
-  </si>
-  <si>
-    <t>7,232</t>
-  </si>
-  <si>
-    <t>14.21%</t>
+    <t>3,262,069</t>
+  </si>
+  <si>
+    <t>5,783</t>
+  </si>
+  <si>
+    <t>6.23%</t>
   </si>
   <si>
     <t>NOK</t>
@@ -391,16 +424,7 @@
     <t>Nokia Corporation Sponsored American Depositary Shares</t>
   </si>
   <si>
-    <t>5,012</t>
-  </si>
-  <si>
-    <t>7,970</t>
-  </si>
-  <si>
-    <t>99,956,310</t>
-  </si>
-  <si>
-    <t>05/14/2026</t>
+    <t>117,907,142</t>
   </si>
   <si>
     <t>04/28/2026</t>
@@ -409,13 +433,13 @@
     <t>05/12/2026</t>
   </si>
   <si>
-    <t>123,435,010</t>
-  </si>
-  <si>
-    <t>96,757</t>
-  </si>
-  <si>
-    <t>2.36%</t>
+    <t>124,610,493</t>
+  </si>
+  <si>
+    <t>80,908</t>
+  </si>
+  <si>
+    <t>4.40%</t>
   </si>
   <si>
     <t>NOW</t>
@@ -424,19 +448,19 @@
     <t>ServiceNow Inc.</t>
   </si>
   <si>
-    <t>18,671,888</t>
+    <t>26,062,434</t>
   </si>
   <si>
     <t>06/02/2026</t>
   </si>
   <si>
-    <t>33,434,912</t>
-  </si>
-  <si>
-    <t>131,607</t>
-  </si>
-  <si>
-    <t>0.83%</t>
+    <t>31,526,437</t>
+  </si>
+  <si>
+    <t>106,275</t>
+  </si>
+  <si>
+    <t>0.76%</t>
   </si>
   <si>
     <t>NOWL</t>
@@ -445,22 +469,19 @@
     <t>GraniteShares 2x Long NOW Daily ETF</t>
   </si>
   <si>
-    <t>11,122</t>
-  </si>
-  <si>
-    <t>12,884</t>
-  </si>
-  <si>
-    <t>24,239,902</t>
-  </si>
-  <si>
-    <t>22,965,784</t>
-  </si>
-  <si>
-    <t>4,523</t>
-  </si>
-  <si>
-    <t>0.92%</t>
+    <t>2,000</t>
+  </si>
+  <si>
+    <t>15,624,219</t>
+  </si>
+  <si>
+    <t>24,626,306</t>
+  </si>
+  <si>
+    <t>4,151</t>
+  </si>
+  <si>
+    <t>0.71%</t>
   </si>
   <si>
     <t>QQQ</t>
@@ -469,7 +490,7 @@
     <t>INVESCO QQQ Trust</t>
   </si>
   <si>
-    <t>19,955,108</t>
+    <t>51,392,504</t>
   </si>
   <si>
     <t>12/23/2025</t>
@@ -481,13 +502,13 @@
     <t>03/27/2026</t>
   </si>
   <si>
-    <t>38,411,776</t>
-  </si>
-  <si>
-    <t>499,256</t>
-  </si>
-  <si>
-    <t>5.09%</t>
+    <t>44,922,493</t>
+  </si>
+  <si>
+    <t>479,251</t>
+  </si>
+  <si>
+    <t>5.34%</t>
   </si>
   <si>
     <t>SLV</t>
@@ -496,88 +517,40 @@
     <t>iShares Silver Trust</t>
   </si>
   <si>
-    <t>7,991,122</t>
-  </si>
-  <si>
-    <t>21,758,328</t>
-  </si>
-  <si>
-    <t>36,514</t>
+    <t>3,316</t>
+  </si>
+  <si>
+    <t>21,280,264</t>
+  </si>
+  <si>
+    <t>23,137,255</t>
+  </si>
+  <si>
+    <t>32,463</t>
   </si>
   <si>
     <t>1.36%</t>
   </si>
   <si>
-    <t>SNDK</t>
-  </si>
-  <si>
-    <t>Sandisk Corporation</t>
-  </si>
-  <si>
-    <t>1,800.665</t>
-  </si>
-  <si>
-    <t>1,800.18</t>
-  </si>
-  <si>
-    <t>1,801.05</t>
-  </si>
-  <si>
-    <t>5,996,226</t>
-  </si>
-  <si>
-    <t>1,716.36</t>
-  </si>
-  <si>
-    <t>1,809.50</t>
-  </si>
-  <si>
-    <t>1,708.88</t>
-  </si>
-  <si>
-    <t>1,804.00</t>
-  </si>
-  <si>
-    <t>3,601.33</t>
-  </si>
-  <si>
-    <t>1,737.015</t>
-  </si>
-  <si>
-    <t>3,474.03</t>
-  </si>
-  <si>
-    <t>1,737.02</t>
-  </si>
-  <si>
-    <t>13,726,077</t>
-  </si>
-  <si>
-    <t>254,175</t>
-  </si>
-  <si>
-    <t>24.66%</t>
-  </si>
-  <si>
     <t>TSLA</t>
   </si>
   <si>
     <t>Tesla Inc.</t>
   </si>
   <si>
-    <t>24,948,645</t>
+    <t>64,004,586</t>
   </si>
   <si>
     <t>12/29/2025</t>
   </si>
   <si>
-    <t>53,903,795</t>
-  </si>
-  <si>
-    <t>1,591,450</t>
-  </si>
-  <si>
-    <t>2.90%</t>
+    <t>51,096,728</t>
+  </si>
+  <si>
+    <t>1,499,097</t>
+  </si>
+  <si>
+    <t>3.00%</t>
   </si>
   <si>
     <t>VOO</t>
@@ -586,16 +559,16 @@
     <t>Vanguard S&amp;P 500 ETF</t>
   </si>
   <si>
-    <t>2,684,606</t>
-  </si>
-  <si>
-    <t>6,073,371</t>
-  </si>
-  <si>
-    <t>931,703</t>
-  </si>
-  <si>
-    <t>4.75%</t>
+    <t>6,461,789</t>
+  </si>
+  <si>
+    <t>7,520,452</t>
+  </si>
+  <si>
+    <t>928,628</t>
+  </si>
+  <si>
+    <t>5.04%</t>
   </si>
 </sst>
 </file>
@@ -1119,52 +1092,52 @@
         <v>41</v>
       </c>
       <c r="E2" t="n">
-        <v>534.1872</v>
+        <v>514.87</v>
       </c>
       <c r="F2" t="n">
-        <v>12.6472</v>
+        <v>26.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42</v>
+        <v>5.41</v>
       </c>
       <c r="H2" t="n">
-        <v>534.22</v>
+        <v>514.52</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>534.55</v>
+        <v>515.85</v>
       </c>
       <c r="K2" t="n">
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="L2" t="s">
         <v>42</v>
       </c>
       <c r="M2" t="n">
-        <v>521.54</v>
+        <v>488.45</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>499.68</v>
       </c>
       <c r="O2" t="n">
-        <v>544.04</v>
+        <v>521.69</v>
       </c>
       <c r="P2" t="n">
-        <v>524.3</v>
+        <v>494</v>
       </c>
       <c r="Q2" t="n">
-        <v>527.2</v>
+        <v>546.44</v>
       </c>
       <c r="R2" t="n">
-        <v>111.01</v>
+        <v>115.06</v>
       </c>
       <c r="S2" t="n">
-        <v>534.19</v>
+        <v>514.87</v>
       </c>
       <c r="T2" t="n">
-        <v>12.65</v>
+        <v>26.42</v>
       </c>
       <c r="U2" t="n">
         <v>415.71</v>
@@ -1173,10 +1146,10 @@
         <v>415.71</v>
       </c>
       <c r="W2" t="n">
-        <v>118.48</v>
+        <v>99.16</v>
       </c>
       <c r="X2" t="n">
-        <v>28.5</v>
+        <v>23.85</v>
       </c>
       <c r="Y2" t="n">
         <v>415.71</v>
@@ -1185,10 +1158,10 @@
         <v>415.71</v>
       </c>
       <c r="AA2" t="n">
-        <v>118.48</v>
+        <v>99.16</v>
       </c>
       <c r="AB2" t="n">
-        <v>28.5</v>
+        <v>23.85</v>
       </c>
       <c r="AC2" t="s">
         <v>43</v>
@@ -1209,7 +1182,7 @@
         <v>3.05</v>
       </c>
       <c r="AI2" t="n">
-        <v>167.26</v>
+        <v>116.23</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -1238,40 +1211,40 @@
         <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>250.17</v>
+        <v>238.65</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.35</v>
+        <v>-2.86</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.48</v>
+        <v>-1.18</v>
       </c>
       <c r="H3" t="n">
-        <v>250.14</v>
+        <v>238.65</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>250.16</v>
+        <v>238.69</v>
       </c>
       <c r="K3" t="n">
-        <v>25</v>
+        <v>850</v>
       </c>
       <c r="L3" t="s">
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>256.52</v>
+        <v>241.51</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>243.21</v>
       </c>
       <c r="O3" t="n">
-        <v>257.09</v>
+        <v>243.33</v>
       </c>
       <c r="P3" t="n">
-        <v>249.11</v>
+        <v>233.59</v>
       </c>
       <c r="Q3" t="n">
         <v>278.56</v>
@@ -1280,10 +1253,10 @@
         <v>196</v>
       </c>
       <c r="S3" t="n">
-        <v>500.34</v>
+        <v>477.3</v>
       </c>
       <c r="T3" t="n">
-        <v>-12.7</v>
+        <v>-5.72</v>
       </c>
       <c r="U3" t="n">
         <v>236.55</v>
@@ -1292,10 +1265,10 @@
         <v>473.1</v>
       </c>
       <c r="W3" t="n">
-        <v>27.24</v>
+        <v>4.2</v>
       </c>
       <c r="X3" t="n">
-        <v>5.76</v>
+        <v>0.89</v>
       </c>
       <c r="Y3" t="n">
         <v>473.1</v>
@@ -1304,10 +1277,10 @@
         <v>236.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>27.24</v>
+        <v>4.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.76</v>
+        <v>0.89</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1325,7 +1298,7 @@
         <v>8.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>36.44</v>
+        <v>31.71</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1354,314 +1327,317 @@
         <v>55</v>
       </c>
       <c r="E4" t="n">
-        <v>41.43</v>
+        <v>382.55</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.8</v>
+        <v>-3.02</v>
       </c>
       <c r="G4" t="n">
-        <v>-12.28</v>
+        <v>-0.78</v>
       </c>
       <c r="H4" t="n">
-        <v>41.4</v>
+        <v>382.45</v>
       </c>
       <c r="I4" t="n">
-        <v>202</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>41.48</v>
-      </c>
-      <c r="K4" t="n">
-        <v>100</v>
+        <v>382.78</v>
+      </c>
+      <c r="K4" t="s">
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M4" t="n">
-        <v>47.23</v>
+        <v>385.57</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>383.72</v>
       </c>
       <c r="O4" t="n">
-        <v>45.41</v>
+        <v>384.98</v>
       </c>
       <c r="P4" t="n">
-        <v>40.7</v>
+        <v>377</v>
       </c>
       <c r="Q4" t="n">
-        <v>72.87</v>
+        <v>495</v>
       </c>
       <c r="R4" t="n">
-        <v>19.71</v>
+        <v>243.8</v>
       </c>
       <c r="S4" t="n">
-        <v>41.43</v>
+        <v>382.55</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.8</v>
+        <v>-3.02</v>
       </c>
       <c r="U4" t="n">
-        <v>49.7</v>
+        <v>375.5</v>
       </c>
       <c r="V4" t="n">
-        <v>49.7</v>
+        <v>375.5</v>
       </c>
       <c r="W4" t="n">
-        <v>-8.27</v>
+        <v>7.05</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.64</v>
+        <v>1.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>49.7</v>
+        <v>375.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>49.7</v>
+        <v>375.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>-8.27</v>
+        <v>7.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>-16.64</v>
+        <v>1.88</v>
       </c>
       <c r="AC4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AF4" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="AI4" t="n">
-        <v>24.42</v>
+        <v>67.41</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.11</v>
+        <v>1.42</v>
       </c>
       <c r="AL4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AM4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AN4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
-        <v>355.84</v>
+        <v>386.1</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.55</v>
+        <v>22.52</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.71</v>
+        <v>6.19</v>
       </c>
       <c r="H5" t="n">
-        <v>355.85</v>
+        <v>386.01</v>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="J5" t="n">
-        <v>355.88</v>
+        <v>386.8</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="L5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M5" t="n">
-        <v>358.39</v>
+        <v>363.58</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>374.27</v>
       </c>
       <c r="O5" t="n">
-        <v>362.5</v>
+        <v>394.5</v>
       </c>
       <c r="P5" t="n">
-        <v>354.72</v>
+        <v>354.19</v>
       </c>
       <c r="Q5" t="n">
-        <v>404.47</v>
+        <v>440</v>
       </c>
       <c r="R5" t="n">
-        <v>163.33</v>
+        <v>76.88</v>
       </c>
       <c r="S5" t="n">
-        <v>711.68</v>
+        <v>386.1</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.1</v>
+        <v>22.52</v>
       </c>
       <c r="U5" t="n">
-        <v>379.19</v>
+        <v>351.15</v>
       </c>
       <c r="V5" t="n">
-        <v>758.38</v>
+        <v>351.15</v>
       </c>
       <c r="W5" t="n">
-        <v>-46.7</v>
+        <v>34.95</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.16</v>
+        <v>9.95</v>
       </c>
       <c r="Y5" t="n">
-        <v>758.38</v>
+        <v>351.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>379.19</v>
+        <v>351.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>-46.7</v>
+        <v>34.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>-6.16</v>
+        <v>9.95</v>
       </c>
       <c r="AC5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>13.11</v>
+        <v>2.11</v>
       </c>
       <c r="AI5" t="n">
-        <v>34.47</v>
+        <v>151.52</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.23</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AM5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AN5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
-        <v>112.28</v>
+        <v>65.5</v>
       </c>
       <c r="F6" t="n">
-        <v>4.35</v>
+        <v>0.38</v>
       </c>
       <c r="G6" t="n">
-        <v>4.03</v>
+        <v>0.58</v>
       </c>
       <c r="H6" t="n">
-        <v>112.28</v>
+        <v>65.47</v>
       </c>
       <c r="I6" t="n">
-        <v>62</v>
+        <v>299</v>
       </c>
       <c r="J6" t="n">
-        <v>112.3</v>
+        <v>67</v>
       </c>
       <c r="K6" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="L6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" t="n">
-        <v>107.93</v>
+        <v>65.12</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>63.75</v>
       </c>
       <c r="O6" t="n">
-        <v>118.29</v>
+        <v>66.17</v>
       </c>
       <c r="P6" t="n">
-        <v>111.53</v>
+        <v>62.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>132.75</v>
+        <v>70.15</v>
       </c>
       <c r="R6" t="n">
-        <v>18.97</v>
+        <v>26.14</v>
       </c>
       <c r="S6" t="n">
-        <v>449.12</v>
+        <v>327.5</v>
       </c>
       <c r="T6" t="n">
-        <v>17.4</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>113.705</v>
+        <v>58.75</v>
       </c>
       <c r="V6" t="n">
-        <v>454.82</v>
+        <v>293.75</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.7</v>
+        <v>33.75</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.25</v>
+        <v>11.49</v>
       </c>
       <c r="Y6" t="n">
-        <v>454.82</v>
+        <v>293.75</v>
       </c>
       <c r="Z6" t="n">
-        <v>113.71</v>
+        <v>58.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>-5.7</v>
+        <v>33.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.25</v>
+        <v>11.49</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>58</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1685,102 +1661,102 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AM6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>949.47</v>
+        <v>29.21</v>
       </c>
       <c r="F7" t="n">
-        <v>-79.68</v>
+        <v>-9.49</v>
       </c>
       <c r="G7" t="n">
-        <v>-7.74</v>
+        <v>-24.52</v>
       </c>
       <c r="H7" t="n">
-        <v>949.47</v>
+        <v>29.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>949.88</v>
+        <v>48</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>78</v>
-      </c>
-      <c r="M7" t="s">
         <v>79</v>
       </c>
+      <c r="M7" t="n">
+        <v>38.7</v>
+      </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
+        <v>38.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="R7" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-9.49</v>
+      </c>
+      <c r="U7" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-20.49</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-41.23</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-20.49</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-41.23</v>
+      </c>
+      <c r="AC7" t="s">
         <v>80</v>
-      </c>
-      <c r="P7" t="n">
-        <v>944.05</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>81</v>
-      </c>
-      <c r="R7" t="n">
-        <v>72.29</v>
-      </c>
-      <c r="S7" t="s">
-        <v>82</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-159.36</v>
-      </c>
-      <c r="U7" t="n">
-        <v>928.56</v>
-      </c>
-      <c r="V7" t="s">
-        <v>83</v>
-      </c>
-      <c r="W7" t="n">
-        <v>41.82</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-553.29</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-22.56</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>86</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1795,819 +1771,816 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>163.36</v>
+        <v>24.42</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.47</v>
+        <v>5.11</v>
       </c>
       <c r="AL7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AM7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="AN7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>359.12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H8" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>28</v>
+      </c>
+      <c r="J8" t="n">
+        <v>365.48</v>
+      </c>
+      <c r="K8" t="n">
+        <v>35</v>
+      </c>
+      <c r="L8" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" t="n">
+        <v>356.56</v>
+      </c>
+      <c r="N8" t="n">
+        <v>361.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>364.77</v>
+      </c>
+      <c r="P8" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>404.47</v>
+      </c>
+      <c r="R8" t="n">
+        <v>163.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>718.24</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>379.19</v>
+      </c>
+      <c r="V8" t="n">
+        <v>758.38</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-40.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>758.38</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>379.19</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-40.14</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM8" t="s">
         <v>91</v>
       </c>
-      <c r="E8" t="s">
+      <c r="AN8" t="s">
         <v>92</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H8" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" t="n">
-        <v>16</v>
-      </c>
-      <c r="J8" t="s">
-        <v>94</v>
-      </c>
-      <c r="K8" t="n">
-        <v>40</v>
-      </c>
-      <c r="L8" t="s">
-        <v>95</v>
-      </c>
-      <c r="M8" t="s">
-        <v>96</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>97</v>
-      </c>
-      <c r="P8" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>99</v>
-      </c>
-      <c r="R8" t="n">
-        <v>94.4</v>
-      </c>
-      <c r="S8" t="s">
-        <v>100</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U8" t="s">
-        <v>101</v>
-      </c>
-      <c r="V8" t="s">
-        <v>102</v>
-      </c>
-      <c r="W8" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>102</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>105</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21.18</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>48.89</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>106</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>107</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="9" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" t="s">
-        <v>111</v>
+        <v>94</v>
+      </c>
+      <c r="E9" t="n">
+        <v>921</v>
       </c>
       <c r="F9" t="n">
-        <v>4.83</v>
+        <v>31.41</v>
       </c>
       <c r="G9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H9" t="s">
-        <v>112</v>
+        <v>3.53</v>
+      </c>
+      <c r="H9" t="n">
+        <v>920</v>
       </c>
       <c r="I9" t="n">
-        <v>240</v>
-      </c>
-      <c r="J9" t="s">
-        <v>111</v>
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>922</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>113</v>
-      </c>
-      <c r="M9" t="s">
-        <v>114</v>
+        <v>95</v>
+      </c>
+      <c r="M9" t="n">
+        <v>889.59</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>115</v>
+        <v>889.42</v>
+      </c>
+      <c r="O9" t="n">
+        <v>934.26</v>
       </c>
       <c r="P9" t="n">
-        <v>985</v>
+        <v>863</v>
       </c>
       <c r="Q9" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R9" t="n">
-        <v>14.6</v>
+        <v>81.04</v>
       </c>
       <c r="S9" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="T9" t="n">
-        <v>40.21</v>
+        <v>62.82</v>
       </c>
       <c r="U9" t="n">
-        <v>986.575</v>
+        <v>874.63</v>
       </c>
       <c r="V9" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="W9" t="n">
-        <v>102.85</v>
+        <v>92.74</v>
       </c>
       <c r="X9" t="n">
-        <v>5.21</v>
+        <v>5.3</v>
       </c>
       <c r="Y9" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>986.58</v>
+        <v>99</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>100</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.85</v>
+        <v>-474.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.21</v>
+        <v>-20.47</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="AF9" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="AI9" t="n">
-        <v>19.25</v>
+        <v>162.87</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>10.56</v>
+        <v>1.47</v>
       </c>
       <c r="AL9" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="AM9" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="AN9" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E10" t="n">
-        <v>17.255</v>
+        <v>281.2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.405</v>
+        <v>0.49</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>0.17</v>
       </c>
       <c r="H10" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="I10" t="s">
-        <v>126</v>
+        <v>281</v>
+      </c>
+      <c r="I10" t="n">
+        <v>35</v>
       </c>
       <c r="J10" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="K10" t="s">
-        <v>127</v>
+        <v>282</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
       </c>
       <c r="L10" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="M10" t="n">
-        <v>16.85</v>
+        <v>280.71</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>269.88</v>
       </c>
       <c r="O10" t="n">
-        <v>17.45</v>
+        <v>287.98</v>
       </c>
       <c r="P10" t="n">
-        <v>16.41</v>
+        <v>267.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>17.11</v>
+        <v>324.2</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>61.44</v>
       </c>
       <c r="S10" t="n">
-        <v>345.1</v>
+        <v>281.2</v>
       </c>
       <c r="T10" t="n">
-        <v>8.1</v>
+        <v>0.49</v>
       </c>
       <c r="U10" t="n">
-        <v>14.75</v>
+        <v>260.74</v>
       </c>
       <c r="V10" t="n">
-        <v>295</v>
+        <v>260.74</v>
       </c>
       <c r="W10" t="n">
-        <v>50.1</v>
+        <v>20.46</v>
       </c>
       <c r="X10" t="n">
-        <v>16.98</v>
+        <v>7.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>295</v>
+        <v>260.74</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.75</v>
+        <v>260.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>50.1</v>
+        <v>20.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.98</v>
+        <v>7.85</v>
       </c>
       <c r="AC10" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="AE10" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="AF10" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.14</v>
+        <v>2.91</v>
       </c>
       <c r="AI10" t="n">
-        <v>114.96</v>
+        <v>25.07</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>0.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.16</v>
+        <v>2.29</v>
       </c>
       <c r="AL10" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="AM10" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" t="n">
+        <v>989.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="H11" t="n">
+        <v>989.5</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" t="n">
-        <v>120.66</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-6.99</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-5.48</v>
-      </c>
-      <c r="H11" t="n">
-        <v>120.62</v>
-      </c>
-      <c r="I11" t="n">
-        <v>24</v>
-      </c>
       <c r="J11" t="n">
-        <v>120.68</v>
+        <v>990</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="L11" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="M11" t="n">
-        <v>127.65</v>
+        <v>995.87</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>128.08</v>
+        <v>971.81</v>
+      </c>
+      <c r="O11" t="s">
+        <v>115</v>
       </c>
       <c r="P11" t="n">
-        <v>119.31</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>211.48</v>
+        <v>960.2</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>116</v>
       </c>
       <c r="R11" t="n">
-        <v>81.24</v>
-      </c>
-      <c r="S11" t="n">
-        <v>120.66</v>
+        <v>103.38</v>
+      </c>
+      <c r="S11" t="s">
+        <v>117</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.99</v>
+        <v>-31.35</v>
       </c>
       <c r="U11" t="n">
-        <v>125.09</v>
-      </c>
-      <c r="V11" t="n">
-        <v>125.09</v>
+        <v>970.472</v>
+      </c>
+      <c r="V11" t="s">
+        <v>118</v>
       </c>
       <c r="W11" t="n">
-        <v>-4.43</v>
+        <v>95.64</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.54</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>125.09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>125.09</v>
+        <v>1.97</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>120</v>
       </c>
       <c r="AA11" t="n">
-        <v>-4.43</v>
+        <v>-928.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.54</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>138</v>
+        <v>-15.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AE11" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="AF11" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.68</v>
+        <v>21.18</v>
       </c>
       <c r="AI11" t="n">
-        <v>81.26</v>
+        <v>24.42</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.94</v>
+        <v>2.17</v>
       </c>
       <c r="AL11" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="AM11" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="AN11" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A12" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="E12" t="n">
-        <v>6.75</v>
+        <v>844.13</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.82</v>
+        <v>-12.61</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.83</v>
+        <v>-1.47</v>
       </c>
       <c r="H12" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="I12" t="s">
-        <v>144</v>
+        <v>835</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="K12" t="s">
-        <v>145</v>
+        <v>855</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="M12" t="n">
-        <v>7.57</v>
+        <v>856.74</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>813.27</v>
       </c>
       <c r="O12" t="n">
-        <v>7.6</v>
+        <v>883</v>
       </c>
       <c r="P12" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>29.01</v>
+        <v>793.89</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>129</v>
       </c>
       <c r="R12" t="n">
-        <v>3.49</v>
+        <v>16.73</v>
       </c>
       <c r="S12" t="n">
-        <v>135</v>
+        <v>844.13</v>
       </c>
       <c r="T12" t="n">
-        <v>-16.4</v>
+        <v>-12.61</v>
       </c>
       <c r="U12" t="n">
-        <v>7.34</v>
+        <v>765.97</v>
       </c>
       <c r="V12" t="n">
-        <v>146.8</v>
+        <v>765.97</v>
       </c>
       <c r="W12" t="n">
-        <v>-11.8</v>
+        <v>78.16</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.04</v>
+        <v>10.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>146.8</v>
+        <v>765.97</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.34</v>
+        <v>765.97</v>
       </c>
       <c r="AA12" t="n">
-        <v>-11.8</v>
+        <v>78.16</v>
       </c>
       <c r="AB12" t="n">
-        <v>-8.04</v>
+        <v>10.2</v>
       </c>
       <c r="AC12" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AE12" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="AF12" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>91.67</v>
+        <v>19.28</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.28</v>
+        <v>10.56</v>
       </c>
       <c r="AL12" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="AM12" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="AN12" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="E13" t="n">
-        <v>743.9578</v>
+        <v>14.89</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2021</v>
+        <v>0.8</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3</v>
+        <v>5.66</v>
       </c>
       <c r="H13" t="n">
-        <v>743.95</v>
+        <v>14.86</v>
       </c>
       <c r="I13" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="J13" t="n">
-        <v>743.97</v>
+        <v>14.92</v>
       </c>
       <c r="K13" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="L13" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="M13" t="n">
-        <v>746.16</v>
+        <v>14.09</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>14.34</v>
       </c>
       <c r="O13" t="n">
-        <v>748.63</v>
+        <v>15.07</v>
       </c>
       <c r="P13" t="n">
-        <v>741.02</v>
+        <v>14.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>746.44</v>
+        <v>17.45</v>
       </c>
       <c r="R13" t="n">
-        <v>515.97</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>743.96</v>
+        <v>595.48</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.2</v>
+        <v>31.88</v>
       </c>
       <c r="U13" t="n">
-        <v>619.5</v>
+        <v>14.3225</v>
       </c>
       <c r="V13" t="n">
-        <v>619.5</v>
+        <v>572.9</v>
       </c>
       <c r="W13" t="n">
-        <v>124.46</v>
+        <v>22.58</v>
       </c>
       <c r="X13" t="n">
-        <v>20.09</v>
+        <v>3.94</v>
       </c>
       <c r="Y13" t="n">
-        <v>619.5</v>
+        <v>572.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>619.5</v>
+        <v>14.32</v>
       </c>
       <c r="AA13" t="n">
-        <v>124.46</v>
+        <v>22.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>20.09</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>153</v>
+        <v>3.94</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.82</v>
+        <v>0.19</v>
       </c>
       <c r="AE13" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="AF13" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.82</v>
+        <v>0.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AI13" t="n">
-        <v>32.42</v>
+        <v>46.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AL13" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="AM13" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="AN13" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A14" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E14" t="n">
-        <v>66.385</v>
+        <v>102.88</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.605</v>
+        <v>-0.2</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.36</v>
+        <v>-0.19</v>
       </c>
       <c r="H14" t="n">
-        <v>66.37</v>
+        <v>100.44</v>
       </c>
       <c r="I14" t="n">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>66.39</v>
+        <v>105.01</v>
       </c>
       <c r="K14" t="n">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="L14" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="M14" t="n">
-        <v>67.99</v>
+        <v>103.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>103.38</v>
       </c>
       <c r="O14" t="n">
-        <v>67.14</v>
+        <v>103.38</v>
       </c>
       <c r="P14" t="n">
-        <v>66.19</v>
+        <v>98.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>109.83</v>
+        <v>211.48</v>
       </c>
       <c r="R14" t="n">
-        <v>30.72</v>
+        <v>81.24</v>
       </c>
       <c r="S14" t="n">
-        <v>199.16</v>
+        <v>102.88</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.81</v>
+        <v>-0.2</v>
       </c>
       <c r="U14" t="n">
-        <v>74.94667</v>
+        <v>125.09</v>
       </c>
       <c r="V14" t="n">
-        <v>224.84</v>
+        <v>125.09</v>
       </c>
       <c r="W14" t="n">
-        <v>-25.68</v>
+        <v>-22.21</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.42</v>
+        <v>-17.76</v>
       </c>
       <c r="Y14" t="n">
-        <v>224.84</v>
+        <v>125.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>74.95</v>
+        <v>125.09</v>
       </c>
       <c r="AA14" t="n">
-        <v>-25.68</v>
+        <v>-22.21</v>
       </c>
       <c r="AB14" t="n">
-        <v>-11.42</v>
+        <v>-17.76</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>146</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2622,108 +2595,111 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>52.63</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.45</v>
+        <v>0.94</v>
       </c>
       <c r="AL14" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="AM14" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="AN14" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A15" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>166</v>
-      </c>
-      <c r="E15" t="s">
-        <v>167</v>
+        <v>151</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.8</v>
       </c>
       <c r="F15" t="n">
-        <v>84.3051</v>
+        <v>-0.05</v>
       </c>
       <c r="G15" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="H15" t="s">
-        <v>168</v>
+        <v>-1.03</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.78</v>
       </c>
       <c r="I15" t="n">
-        <v>52</v>
-      </c>
-      <c r="J15" t="s">
-        <v>169</v>
-      </c>
-      <c r="K15" t="n">
-        <v>30</v>
+        <v>60</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="K15" t="s">
+        <v>152</v>
       </c>
       <c r="L15" t="s">
-        <v>170</v>
-      </c>
-      <c r="M15" t="s">
-        <v>171</v>
+        <v>153</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.85</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>172</v>
-      </c>
-      <c r="P15" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>174</v>
+        <v>4.85</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>29.01</v>
       </c>
       <c r="R15" t="n">
-        <v>36.21</v>
-      </c>
-      <c r="S15" t="s">
-        <v>175</v>
+        <v>3.49</v>
+      </c>
+      <c r="S15" t="n">
+        <v>96</v>
       </c>
       <c r="T15" t="n">
-        <v>168.61</v>
-      </c>
-      <c r="U15" t="s">
-        <v>176</v>
-      </c>
-      <c r="V15" t="s">
-        <v>177</v>
+        <v>-1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="V15" t="n">
+        <v>146.8</v>
       </c>
       <c r="W15" t="n">
-        <v>127.3</v>
+        <v>-50.8</v>
       </c>
       <c r="X15" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>178</v>
+        <v>-34.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>127.3</v>
+        <v>-50.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.66</v>
+        <v>-34.6</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>146</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2738,263 +2714,498 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>29.48</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>61.35</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>4.88</v>
+        <v>1.28</v>
       </c>
       <c r="AL15" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="AM15" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="AN15" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="E16" t="n">
-        <v>424.14</v>
+        <v>722.98</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4</v>
+        <v>5.86</v>
       </c>
       <c r="G16" t="n">
-        <v>0.09</v>
+        <v>0.82</v>
       </c>
       <c r="H16" t="n">
-        <v>424.11</v>
+        <v>723.12</v>
       </c>
       <c r="I16" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>424.17</v>
+        <v>723.36</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="M16" t="n">
-        <v>423.74</v>
+        <v>717.12</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>717.61</v>
       </c>
       <c r="O16" t="n">
-        <v>433.6</v>
+        <v>724.01</v>
       </c>
       <c r="P16" t="n">
-        <v>416</v>
+        <v>711.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>498.83</v>
+        <v>748.65</v>
       </c>
       <c r="R16" t="n">
-        <v>273.21</v>
+        <v>523.65</v>
       </c>
       <c r="S16" t="n">
-        <v>424.14</v>
+        <v>722.98</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4</v>
+        <v>5.86</v>
       </c>
       <c r="U16" t="n">
-        <v>468.88</v>
+        <v>619.5</v>
       </c>
       <c r="V16" t="n">
-        <v>468.88</v>
+        <v>619.5</v>
       </c>
       <c r="W16" t="n">
-        <v>-44.74</v>
+        <v>103.48</v>
       </c>
       <c r="X16" t="n">
-        <v>-9.54</v>
+        <v>16.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>468.88</v>
+        <v>619.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>468.88</v>
+        <v>619.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>-44.74</v>
+        <v>103.48</v>
       </c>
       <c r="AB16" t="n">
-        <v>-9.54</v>
+        <v>16.7</v>
       </c>
       <c r="AC16" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE16" t="s">
-        <v>44</v>
+        <v>161</v>
       </c>
       <c r="AF16" t="s">
-        <v>44</v>
+        <v>162</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>381.54</v>
+        <v>32.42</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="AL16" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="AM16" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="AN16" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A17" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>167</v>
+      </c>
+      <c r="E17" t="n">
+        <v>61.47</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H17" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>61.47</v>
+      </c>
+      <c r="K17" t="s">
+        <v>168</v>
+      </c>
+      <c r="L17" t="s">
+        <v>169</v>
+      </c>
+      <c r="M17" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="N17" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="O17" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="P17" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>109.83</v>
+      </c>
+      <c r="R17" t="n">
+        <v>32.06</v>
+      </c>
+      <c r="S17" t="n">
+        <v>184.41</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U17" t="n">
+        <v>74.94667</v>
+      </c>
+      <c r="V17" t="n">
+        <v>224.84</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-40.43</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-17.98</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>224.84</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-40.43</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-17.98</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>170</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>171</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" collapsed="0" hidden="0" customHeight="0" spans="1:1">
+      <c r="A18" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="s">
-        <v>190</v>
-      </c>
-      <c r="E17" t="n">
-        <v>694.48</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="H17" t="n">
-        <v>694.47</v>
-      </c>
-      <c r="I17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>694.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>41</v>
-      </c>
-      <c r="L17" t="s">
-        <v>191</v>
-      </c>
-      <c r="M17" t="n">
-        <v>698.26</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>697.65</v>
-      </c>
-      <c r="P17" t="n">
-        <v>693.95</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="D18" t="s">
+        <v>174</v>
+      </c>
+      <c r="E18" t="n">
+        <v>406.1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H18" t="n">
+        <v>406.01</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" t="n">
+        <v>406.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>19</v>
+      </c>
+      <c r="L18" t="s">
+        <v>175</v>
+      </c>
+      <c r="M18" t="n">
+        <v>399.15</v>
+      </c>
+      <c r="N18" t="n">
+        <v>399.46</v>
+      </c>
+      <c r="O18" t="n">
+        <v>406.68</v>
+      </c>
+      <c r="P18" t="n">
+        <v>386.76</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>498.83</v>
+      </c>
+      <c r="R18" t="n">
+        <v>288.77</v>
+      </c>
+      <c r="S18" t="n">
+        <v>406.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="U18" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="V18" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-62.78</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-13.39</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-62.78</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-13.39</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>350.12</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>177</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>178</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" collapsed="0" hidden="0" customHeight="0" spans="1:1">
+      <c r="A19" t="s">
+        <v>180</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E19" t="n">
+        <v>682.68</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H19" t="n">
+        <v>682.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>682.84</v>
+      </c>
+      <c r="K19" t="n">
+        <v>13</v>
+      </c>
+      <c r="L19" t="s">
+        <v>182</v>
+      </c>
+      <c r="M19" t="n">
+        <v>678.23</v>
+      </c>
+      <c r="N19" t="n">
+        <v>681.07</v>
+      </c>
+      <c r="O19" t="n">
+        <v>684.44</v>
+      </c>
+      <c r="P19" t="n">
+        <v>675.84</v>
+      </c>
+      <c r="Q19" t="n">
         <v>699.15</v>
       </c>
-      <c r="R17" t="n">
-        <v>537.8</v>
-      </c>
-      <c r="S17" t="n">
-        <v>694.48</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="R19" t="n">
+        <v>545.75</v>
+      </c>
+      <c r="S19" t="n">
+        <v>682.68</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="U19" t="n">
         <v>629.5</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V19" t="n">
         <v>629.5</v>
       </c>
-      <c r="W17" t="n">
-        <v>64.98</v>
-      </c>
-      <c r="X17" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="W19" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8.45</v>
+      </c>
+      <c r="Y19" t="n">
         <v>629.5</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z19" t="n">
         <v>629.5</v>
       </c>
-      <c r="AA17" t="n">
-        <v>64.98</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>153</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AA19" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.45</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>160</v>
+      </c>
+      <c r="AD19" t="n">
         <v>7.13</v>
       </c>
-      <c r="AE17" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AE19" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG19" t="n">
         <v>7.13</v>
       </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>26.4</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK17" t="n">
+      <c r="AJ19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1</v>
       </c>
-      <c r="AL17" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>193</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>194</v>
+      <c r="AL19" t="s">
+        <v>183</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>184</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/data/67744964-positions.xlsx
+++ b/data/67744964-positions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
   <si>
     <t>代號</t>
   </si>
@@ -133,28 +133,58 @@
     <t>持倉佔比</t>
   </si>
   <si>
+    <t>AAOI</t>
+  </si>
+  <si>
+    <t>Applied Optoelectronics Inc.</t>
+  </si>
+  <si>
+    <t>-5.36%</t>
+  </si>
+  <si>
+    <t>5,668,107</t>
+  </si>
+  <si>
+    <t>-20.74%</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>13,340,843</t>
+  </si>
+  <si>
+    <t>11,117</t>
+  </si>
+  <si>
+    <t>1.14%</t>
+  </si>
+  <si>
     <t>AMD</t>
   </si>
   <si>
     <t>Advanced Micro Devices Inc.</t>
   </si>
   <si>
-    <t>31,674,258</t>
+    <t>-2.78%</t>
+  </si>
+  <si>
+    <t>13,398,004</t>
+  </si>
+  <si>
+    <t>24.55%</t>
   </si>
   <si>
     <t>05/19/2026</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>37,397,056</t>
-  </si>
-  <si>
-    <t>796,467</t>
-  </si>
-  <si>
-    <t>3.80%</t>
+    <t>31,247,843</t>
+  </si>
+  <si>
+    <t>868,409</t>
+  </si>
+  <si>
+    <t>2.25%</t>
   </si>
   <si>
     <t>AMZN</t>
@@ -163,16 +193,22 @@
     <t>Amazon.com Inc.</t>
   </si>
   <si>
-    <t>51,323,825</t>
-  </si>
-  <si>
-    <t>42,897,561</t>
-  </si>
-  <si>
-    <t>2,597,949</t>
-  </si>
-  <si>
-    <t>3.52%</t>
+    <t>1.87%</t>
+  </si>
+  <si>
+    <t>31,125,419</t>
+  </si>
+  <si>
+    <t>-2.24%</t>
+  </si>
+  <si>
+    <t>45,947,300</t>
+  </si>
+  <si>
+    <t>2,441,971</t>
+  </si>
+  <si>
+    <t>2.01%</t>
   </si>
   <si>
     <t>AVGO</t>
@@ -181,10 +217,13 @@
     <t>Broadcom Inc.</t>
   </si>
   <si>
-    <t>1,250</t>
-  </si>
-  <si>
-    <t>27,665,686</t>
+    <t>-2.08%</t>
+  </si>
+  <si>
+    <t>11,121,298</t>
+  </si>
+  <si>
+    <t>-1.19%</t>
   </si>
   <si>
     <t>06/10/2026</t>
@@ -196,13 +235,13 @@
     <t>06/30/2026</t>
   </si>
   <si>
-    <t>27,014,158</t>
-  </si>
-  <si>
-    <t>1,834,380</t>
-  </si>
-  <si>
-    <t>2.83%</t>
+    <t>30,975,554</t>
+  </si>
+  <si>
+    <t>1,802,695</t>
+  </si>
+  <si>
+    <t>1.61%</t>
   </si>
   <si>
     <t>COHR</t>
@@ -211,19 +250,25 @@
     <t>Coherent Corp.</t>
   </si>
   <si>
-    <t>5,391,187</t>
+    <t>-6.88%</t>
+  </si>
+  <si>
+    <t>2,481,799</t>
+  </si>
+  <si>
+    <t>8.00%</t>
   </si>
   <si>
     <t>06/11/2026</t>
   </si>
   <si>
-    <t>6,484,562</t>
-  </si>
-  <si>
-    <t>71,131</t>
-  </si>
-  <si>
-    <t>2.85%</t>
+    <t>5,971,234</t>
+  </si>
+  <si>
+    <t>79,674</t>
+  </si>
+  <si>
+    <t>1.65%</t>
   </si>
   <si>
     <t>DRAM</t>
@@ -232,37 +277,22 @@
     <t>Roundhill Memory</t>
   </si>
   <si>
-    <t>32,329,721</t>
-  </si>
-  <si>
-    <t>39,891,679</t>
-  </si>
-  <si>
-    <t>16,822</t>
-  </si>
-  <si>
-    <t>2.42%</t>
-  </si>
-  <si>
-    <t>DXYZ</t>
-  </si>
-  <si>
-    <t>Destiny Tech100 Inc.</t>
-  </si>
-  <si>
-    <t>16,532,085</t>
-  </si>
-  <si>
-    <t>05/29/2026</t>
-  </si>
-  <si>
-    <t>6,308,942</t>
-  </si>
-  <si>
-    <t>14,706</t>
-  </si>
-  <si>
-    <t>0.22%</t>
+    <t>-4.23%</t>
+  </si>
+  <si>
+    <t>33,631,454</t>
+  </si>
+  <si>
+    <t>18.13%</t>
+  </si>
+  <si>
+    <t>45,840,001</t>
+  </si>
+  <si>
+    <t>21,053</t>
+  </si>
+  <si>
+    <t>2.24%</t>
   </si>
   <si>
     <t>GOOG</t>
@@ -271,7 +301,13 @@
     <t>Alphabet Inc.</t>
   </si>
   <si>
-    <t>17,681,300</t>
+    <t>-0.21%</t>
+  </si>
+  <si>
+    <t>9,441,271</t>
+  </si>
+  <si>
+    <t>-9.95%</t>
   </si>
   <si>
     <t>05/01/2026</t>
@@ -283,13 +319,13 @@
     <t>06/15/2026</t>
   </si>
   <si>
-    <t>22,570,713</t>
-  </si>
-  <si>
-    <t>4,334,741</t>
-  </si>
-  <si>
-    <t>5.30%</t>
+    <t>22,883,674</t>
+  </si>
+  <si>
+    <t>4,164,390</t>
+  </si>
+  <si>
+    <t>2.97%</t>
   </si>
   <si>
     <t>LITE</t>
@@ -298,31 +334,40 @@
     <t>Lumentum Holdings Inc.</t>
   </si>
   <si>
-    <t>4,571,224</t>
+    <t>-8.03%</t>
+  </si>
+  <si>
+    <t>3,213,218</t>
   </si>
   <si>
     <t>1,085.68</t>
   </si>
   <si>
-    <t>1,842.00</t>
+    <t>1,585.50</t>
   </si>
   <si>
     <t>1,749.26</t>
   </si>
   <si>
+    <t>-9.36%</t>
+  </si>
+  <si>
     <t>2,316.08</t>
   </si>
   <si>
     <t>1,158.04</t>
   </si>
   <si>
-    <t>6,323,631</t>
-  </si>
-  <si>
-    <t>69,210</t>
-  </si>
-  <si>
-    <t>13.60%</t>
+    <t>-31.54%</t>
+  </si>
+  <si>
+    <t>5,861,144</t>
+  </si>
+  <si>
+    <t>67,061</t>
+  </si>
+  <si>
+    <t>6.89%</t>
   </si>
   <si>
     <t>MRVL</t>
@@ -331,7 +376,13 @@
     <t>Marvell Technology Inc.</t>
   </si>
   <si>
-    <t>42,185,699</t>
+    <t>-5.08%</t>
+  </si>
+  <si>
+    <t>14,305,635</t>
+  </si>
+  <si>
+    <t>-2.22%</t>
   </si>
   <si>
     <t>04/10/2026</t>
@@ -340,13 +391,13 @@
     <t>04/30/2026</t>
   </si>
   <si>
-    <t>43,571,811</t>
-  </si>
-  <si>
-    <t>245,565</t>
-  </si>
-  <si>
-    <t>2.08%</t>
+    <t>58,467,367</t>
+  </si>
+  <si>
+    <t>246,046</t>
+  </si>
+  <si>
+    <t>3.48%</t>
   </si>
   <si>
     <t>MU</t>
@@ -355,40 +406,58 @@
     <t>Micron Technology Inc.</t>
   </si>
   <si>
-    <t>41,085,617</t>
-  </si>
-  <si>
-    <t>1,012.62</t>
-  </si>
-  <si>
-    <t>1,089.29</t>
-  </si>
-  <si>
-    <t>4,948.00</t>
-  </si>
-  <si>
-    <t>4,852.36</t>
-  </si>
-  <si>
-    <t>5,876.36</t>
-  </si>
-  <si>
-    <t>1,175.27</t>
-  </si>
-  <si>
-    <t>03/30/2026</t>
-  </si>
-  <si>
-    <t>04/15/2026</t>
-  </si>
-  <si>
-    <t>55,392,828</t>
-  </si>
-  <si>
-    <t>1,123,077</t>
-  </si>
-  <si>
-    <t>36.54%</t>
+    <t>1,171.17</t>
+  </si>
+  <si>
+    <t>-3.49%</t>
+  </si>
+  <si>
+    <t>1,172.00</t>
+  </si>
+  <si>
+    <t>31,613,093</t>
+  </si>
+  <si>
+    <t>1,213.56</t>
+  </si>
+  <si>
+    <t>1,198.71</t>
+  </si>
+  <si>
+    <t>1,126.87</t>
+  </si>
+  <si>
+    <t>1,255.00</t>
+  </si>
+  <si>
+    <t>10,540.53</t>
+  </si>
+  <si>
+    <t>1,172.15557</t>
+  </si>
+  <si>
+    <t>10,549.40</t>
+  </si>
+  <si>
+    <t>-0.08%</t>
+  </si>
+  <si>
+    <t>1,172.16</t>
+  </si>
+  <si>
+    <t>07/06/2026</t>
+  </si>
+  <si>
+    <t>07/21/2026</t>
+  </si>
+  <si>
+    <t>55,635,140</t>
+  </si>
+  <si>
+    <t>1,368,573</t>
+  </si>
+  <si>
+    <t>45.79%</t>
   </si>
   <si>
     <t>MUU</t>
@@ -397,25 +466,49 @@
     <t>Direxion Daily MU Bull 2X Shares</t>
   </si>
   <si>
-    <t>2,876,627</t>
-  </si>
-  <si>
-    <t>1,081.71</t>
-  </si>
-  <si>
-    <t>03/24/2026</t>
-  </si>
-  <si>
-    <t>03/31/2026</t>
-  </si>
-  <si>
-    <t>3,262,069</t>
-  </si>
-  <si>
-    <t>5,783</t>
-  </si>
-  <si>
-    <t>6.23%</t>
+    <t>1,097.82</t>
+  </si>
+  <si>
+    <t>-7.15%</t>
+  </si>
+  <si>
+    <t>1,102.05</t>
+  </si>
+  <si>
+    <t>1,104.82</t>
+  </si>
+  <si>
+    <t>2,416,911</t>
+  </si>
+  <si>
+    <t>1,182.40</t>
+  </si>
+  <si>
+    <t>1,156.71</t>
+  </si>
+  <si>
+    <t>1,012.57</t>
+  </si>
+  <si>
+    <t>1,252.80</t>
+  </si>
+  <si>
+    <t>1,010.70</t>
+  </si>
+  <si>
+    <t>8.62%</t>
+  </si>
+  <si>
+    <t>06/23/2026</t>
+  </si>
+  <si>
+    <t>3,477,114</t>
+  </si>
+  <si>
+    <t>8,159</t>
+  </si>
+  <si>
+    <t>4.77%</t>
   </si>
   <si>
     <t>NOK</t>
@@ -424,7 +517,25 @@
     <t>Nokia Corporation Sponsored American Depositary Shares</t>
   </si>
   <si>
-    <t>117,907,142</t>
+    <t>-8.01%</t>
+  </si>
+  <si>
+    <t>4,934</t>
+  </si>
+  <si>
+    <t>6,680</t>
+  </si>
+  <si>
+    <t>67,857,890</t>
+  </si>
+  <si>
+    <t>1,543.19</t>
+  </si>
+  <si>
+    <t>1,646.70</t>
+  </si>
+  <si>
+    <t>-6.29%</t>
   </si>
   <si>
     <t>04/28/2026</t>
@@ -433,13 +544,13 @@
     <t>05/12/2026</t>
   </si>
   <si>
-    <t>124,610,493</t>
-  </si>
-  <si>
-    <t>80,908</t>
-  </si>
-  <si>
-    <t>4.40%</t>
+    <t>120,513,438</t>
+  </si>
+  <si>
+    <t>80,277</t>
+  </si>
+  <si>
+    <t>6.70%</t>
   </si>
   <si>
     <t>NOW</t>
@@ -448,19 +559,25 @@
     <t>ServiceNow Inc.</t>
   </si>
   <si>
-    <t>26,062,434</t>
+    <t>8.36%</t>
+  </si>
+  <si>
+    <t>11,851,670</t>
+  </si>
+  <si>
+    <t>-22.45%</t>
   </si>
   <si>
     <t>06/02/2026</t>
   </si>
   <si>
-    <t>31,526,437</t>
-  </si>
-  <si>
-    <t>106,275</t>
-  </si>
-  <si>
-    <t>0.76%</t>
+    <t>32,239,292</t>
+  </si>
+  <si>
+    <t>92,295</t>
+  </si>
+  <si>
+    <t>0.42%</t>
   </si>
   <si>
     <t>NOWL</t>
@@ -469,19 +586,28 @@
     <t>GraniteShares 2x Long NOW Daily ETF</t>
   </si>
   <si>
-    <t>2,000</t>
-  </si>
-  <si>
-    <t>15,624,219</t>
-  </si>
-  <si>
-    <t>24,626,306</t>
-  </si>
-  <si>
-    <t>4,151</t>
-  </si>
-  <si>
-    <t>0.71%</t>
+    <t>16.85%</t>
+  </si>
+  <si>
+    <t>43,709</t>
+  </si>
+  <si>
+    <t>50,884</t>
+  </si>
+  <si>
+    <t>18,173,178</t>
+  </si>
+  <si>
+    <t>-42.85%</t>
+  </si>
+  <si>
+    <t>25,358,166</t>
+  </si>
+  <si>
+    <t>3,887</t>
+  </si>
+  <si>
+    <t>0.36%</t>
   </si>
   <si>
     <t>QQQ</t>
@@ -490,25 +616,28 @@
     <t>INVESCO QQQ Trust</t>
   </si>
   <si>
-    <t>51,392,504</t>
+    <t>-0.74%</t>
+  </si>
+  <si>
+    <t>19,678,894</t>
+  </si>
+  <si>
+    <t>14.78%</t>
   </si>
   <si>
     <t>12/23/2025</t>
   </si>
   <si>
-    <t>03/23/2026</t>
-  </si>
-  <si>
-    <t>03/27/2026</t>
-  </si>
-  <si>
-    <t>44,922,493</t>
-  </si>
-  <si>
-    <t>479,251</t>
-  </si>
-  <si>
-    <t>5.34%</t>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>47,744,131</t>
+  </si>
+  <si>
+    <t>477,073</t>
+  </si>
+  <si>
+    <t>3.09%</t>
   </si>
   <si>
     <t>SLV</t>
@@ -517,19 +646,76 @@
     <t>iShares Silver Trust</t>
   </si>
   <si>
-    <t>3,316</t>
-  </si>
-  <si>
-    <t>21,280,264</t>
-  </si>
-  <si>
-    <t>23,137,255</t>
-  </si>
-  <si>
-    <t>32,463</t>
-  </si>
-  <si>
-    <t>1.36%</t>
+    <t>2.33%</t>
+  </si>
+  <si>
+    <t>10,191,350</t>
+  </si>
+  <si>
+    <t>-28.51%</t>
+  </si>
+  <si>
+    <t>23,720,318</t>
+  </si>
+  <si>
+    <t>27,840</t>
+  </si>
+  <si>
+    <t>0.70%</t>
+  </si>
+  <si>
+    <t>SNDK</t>
+  </si>
+  <si>
+    <t>Sandisk Corporation</t>
+  </si>
+  <si>
+    <t>2,152.44</t>
+  </si>
+  <si>
+    <t>-7.82%</t>
+  </si>
+  <si>
+    <t>2,152.00</t>
+  </si>
+  <si>
+    <t>2,153.17</t>
+  </si>
+  <si>
+    <t>6,409,775</t>
+  </si>
+  <si>
+    <t>2,335.00</t>
+  </si>
+  <si>
+    <t>2,256.11</t>
+  </si>
+  <si>
+    <t>2,126.12</t>
+  </si>
+  <si>
+    <t>2,354.39</t>
+  </si>
+  <si>
+    <t>2,141.91992</t>
+  </si>
+  <si>
+    <t>2,141.92</t>
+  </si>
+  <si>
+    <t>0.49%</t>
+  </si>
+  <si>
+    <t>06/26/2026</t>
+  </si>
+  <si>
+    <t>11,324,514</t>
+  </si>
+  <si>
+    <t>345,790</t>
+  </si>
+  <si>
+    <t>9.35%</t>
   </si>
   <si>
     <t>TSLA</t>
@@ -538,19 +724,25 @@
     <t>Tesla Inc.</t>
   </si>
   <si>
-    <t>64,004,586</t>
+    <t>2.12%</t>
+  </si>
+  <si>
+    <t>22,415,075</t>
+  </si>
+  <si>
+    <t>-18.30%</t>
   </si>
   <si>
     <t>12/29/2025</t>
   </si>
   <si>
-    <t>51,096,728</t>
-  </si>
-  <si>
-    <t>1,499,097</t>
-  </si>
-  <si>
-    <t>3.00%</t>
+    <t>47,194,739</t>
+  </si>
+  <si>
+    <t>1,408,847</t>
+  </si>
+  <si>
+    <t>1.66%</t>
   </si>
   <si>
     <t>VOO</t>
@@ -559,16 +751,22 @@
     <t>Vanguard S&amp;P 500 ETF</t>
   </si>
   <si>
-    <t>6,461,789</t>
-  </si>
-  <si>
-    <t>7,520,452</t>
-  </si>
-  <si>
-    <t>928,628</t>
-  </si>
-  <si>
-    <t>5.04%</t>
+    <t>0.02%</t>
+  </si>
+  <si>
+    <t>2,539,130</t>
+  </si>
+  <si>
+    <t>7.05%</t>
+  </si>
+  <si>
+    <t>10,261,876</t>
+  </si>
+  <si>
+    <t>976,765</t>
+  </si>
+  <si>
+    <t>2.93%</t>
   </si>
 </sst>
 </file>
@@ -1086,686 +1284,680 @@
         <v>40</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
         <v>41</v>
       </c>
       <c r="E2" t="n">
-        <v>514.87</v>
+        <v>131.12</v>
       </c>
       <c r="F2" t="n">
-        <v>26.42</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5.41</v>
+        <v>-7.42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>42</v>
       </c>
       <c r="H2" t="n">
-        <v>514.52</v>
+        <v>130.86</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>515.85</v>
+        <v>131.12</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M2" t="n">
-        <v>488.45</v>
+        <v>138.54</v>
       </c>
       <c r="N2" t="n">
-        <v>499.68</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>521.69</v>
+        <v>133.19</v>
       </c>
       <c r="P2" t="n">
-        <v>494</v>
+        <v>127.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>546.44</v>
+        <v>233.67</v>
       </c>
       <c r="R2" t="n">
-        <v>115.06</v>
+        <v>18.5</v>
       </c>
       <c r="S2" t="n">
-        <v>514.87</v>
+        <v>262.24</v>
       </c>
       <c r="T2" t="n">
-        <v>26.42</v>
+        <v>-14.84</v>
       </c>
       <c r="U2" t="n">
-        <v>415.71</v>
+        <v>165.43</v>
       </c>
       <c r="V2" t="n">
-        <v>415.71</v>
+        <v>330.86</v>
       </c>
       <c r="W2" t="n">
-        <v>99.16</v>
-      </c>
-      <c r="X2" t="n">
-        <v>23.85</v>
+        <v>-68.62</v>
+      </c>
+      <c r="X2" t="s">
+        <v>44</v>
       </c>
       <c r="Y2" t="n">
-        <v>415.71</v>
+        <v>330.86</v>
       </c>
       <c r="Z2" t="n">
-        <v>415.71</v>
+        <v>165.43</v>
       </c>
       <c r="AA2" t="n">
-        <v>99.16</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>43</v>
+        <v>-68.62</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>44</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>116.23</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.5</v>
+        <v>3.66</v>
       </c>
       <c r="AL2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AN2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="n">
+        <v>517.79</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" t="n">
+        <v>517.54</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>517.93</v>
+      </c>
+      <c r="K3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" t="n">
-        <v>238.65</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="H3" t="n">
-        <v>238.65</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>238.69</v>
-      </c>
-      <c r="K3" t="n">
-        <v>850</v>
-      </c>
       <c r="L3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M3" t="n">
-        <v>241.51</v>
+        <v>532.57</v>
       </c>
       <c r="N3" t="n">
-        <v>243.21</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>243.33</v>
+        <v>525.11</v>
       </c>
       <c r="P3" t="n">
-        <v>233.59</v>
+        <v>502.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>278.56</v>
+        <v>562.99</v>
       </c>
       <c r="R3" t="n">
-        <v>196</v>
+        <v>133.5</v>
       </c>
       <c r="S3" t="n">
-        <v>477.3</v>
+        <v>517.79</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.72</v>
+        <v>-14.79</v>
       </c>
       <c r="U3" t="n">
-        <v>236.55</v>
+        <v>415.71</v>
       </c>
       <c r="V3" t="n">
-        <v>473.1</v>
+        <v>415.71</v>
       </c>
       <c r="W3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.89</v>
+        <v>102.07</v>
+      </c>
+      <c r="X3" t="s">
+        <v>53</v>
       </c>
       <c r="Y3" t="n">
-        <v>473.1</v>
+        <v>415.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>236.55</v>
+        <v>415.71</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.89</v>
+        <v>102.07</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>54</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>8.36</v>
+        <v>3.05</v>
       </c>
       <c r="AI3" t="n">
-        <v>31.71</v>
+        <v>116.23</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AN3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>382.55</v>
+        <v>231.26</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.02</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.78</v>
+        <v>4.25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>60</v>
       </c>
       <c r="H4" t="n">
-        <v>382.45</v>
+        <v>231.21</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="J4" t="n">
-        <v>382.78</v>
-      </c>
-      <c r="K4" t="s">
-        <v>56</v>
+        <v>231.26</v>
+      </c>
+      <c r="K4" t="n">
+        <v>401</v>
       </c>
       <c r="L4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M4" t="n">
-        <v>385.57</v>
+        <v>227.01</v>
       </c>
       <c r="N4" t="n">
-        <v>383.72</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>384.98</v>
+        <v>232.6</v>
       </c>
       <c r="P4" t="n">
-        <v>377</v>
+        <v>226.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>495</v>
+        <v>278.56</v>
       </c>
       <c r="R4" t="n">
-        <v>243.8</v>
+        <v>196</v>
       </c>
       <c r="S4" t="n">
-        <v>382.55</v>
+        <v>462.52</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.02</v>
+        <v>8.5</v>
       </c>
       <c r="U4" t="n">
-        <v>375.5</v>
+        <v>236.55</v>
       </c>
       <c r="V4" t="n">
-        <v>375.5</v>
+        <v>473.1</v>
       </c>
       <c r="W4" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.88</v>
+        <v>-10.58</v>
+      </c>
+      <c r="X4" t="s">
+        <v>62</v>
       </c>
       <c r="Y4" t="n">
-        <v>375.5</v>
+        <v>473.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>375.5</v>
+        <v>236.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>58</v>
+        <v>-10.58</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>62</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="AF4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.01</v>
+        <v>8.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>67.41</v>
+        <v>31.71</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AM4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AN4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E5" t="n">
-        <v>386.1</v>
+        <v>371.05</v>
       </c>
       <c r="F5" t="n">
-        <v>22.52</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.19</v>
+        <v>-7.86</v>
+      </c>
+      <c r="G5" t="s">
+        <v>68</v>
       </c>
       <c r="H5" t="n">
-        <v>386.01</v>
+        <v>370.97</v>
       </c>
       <c r="I5" t="n">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="J5" t="n">
-        <v>386.8</v>
+        <v>371.3</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M5" t="n">
-        <v>363.58</v>
+        <v>378.91</v>
       </c>
       <c r="N5" t="n">
-        <v>374.27</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>394.5</v>
+        <v>373.69</v>
       </c>
       <c r="P5" t="n">
-        <v>354.19</v>
+        <v>365.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>440</v>
+        <v>495</v>
       </c>
       <c r="R5" t="n">
-        <v>76.88</v>
+        <v>262.66</v>
       </c>
       <c r="S5" t="n">
-        <v>386.1</v>
+        <v>371.05</v>
       </c>
       <c r="T5" t="n">
-        <v>22.52</v>
+        <v>-7.86</v>
       </c>
       <c r="U5" t="n">
-        <v>351.15</v>
+        <v>375.5</v>
       </c>
       <c r="V5" t="n">
-        <v>351.15</v>
+        <v>375.5</v>
       </c>
       <c r="W5" t="n">
-        <v>34.95</v>
-      </c>
-      <c r="X5" t="n">
-        <v>9.95</v>
+        <v>-4.45</v>
+      </c>
+      <c r="X5" t="s">
+        <v>70</v>
       </c>
       <c r="Y5" t="n">
-        <v>351.15</v>
+        <v>375.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>351.15</v>
+        <v>375.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>34.95</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>9.95</v>
+        <v>-4.45</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>70</v>
       </c>
       <c r="AC5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE5" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="AF5" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.11</v>
+        <v>6.01</v>
       </c>
       <c r="AI5" t="n">
-        <v>151.52</v>
+        <v>67.41</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>0.69</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="AL5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="AM5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E6" t="n">
-        <v>65.5</v>
+        <v>379.24</v>
       </c>
       <c r="F6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.58</v>
+        <v>-28.01</v>
+      </c>
+      <c r="G6" t="s">
+        <v>79</v>
       </c>
       <c r="H6" t="n">
-        <v>65.47</v>
+        <v>379.16</v>
       </c>
       <c r="I6" t="n">
-        <v>299</v>
+        <v>16</v>
       </c>
       <c r="J6" t="n">
-        <v>67</v>
+        <v>379.64</v>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>65.12</v>
+        <v>407.25</v>
       </c>
       <c r="N6" t="n">
-        <v>63.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>66.17</v>
+        <v>393.39</v>
       </c>
       <c r="P6" t="n">
-        <v>62.95</v>
+        <v>368.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>70.15</v>
+        <v>440</v>
       </c>
       <c r="R6" t="n">
-        <v>26.14</v>
+        <v>81.61</v>
       </c>
       <c r="S6" t="n">
-        <v>327.5</v>
+        <v>379.24</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>-28.01</v>
       </c>
       <c r="U6" t="n">
-        <v>58.75</v>
+        <v>351.15</v>
       </c>
       <c r="V6" t="n">
-        <v>293.75</v>
+        <v>351.15</v>
       </c>
       <c r="W6" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11.49</v>
+        <v>28.09</v>
+      </c>
+      <c r="X6" t="s">
+        <v>81</v>
       </c>
       <c r="Y6" t="n">
-        <v>293.75</v>
+        <v>351.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>58.75</v>
+        <v>351.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>11.49</v>
+        <v>28.09</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>81</v>
       </c>
       <c r="AC6" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>151.52</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL6" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AM6" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AN6" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E7" t="n">
-        <v>29.21</v>
+        <v>73.64</v>
       </c>
       <c r="F7" t="n">
-        <v>-9.49</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-24.52</v>
+        <v>-3.25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>29.2</v>
+        <v>73.61</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="J7" t="n">
-        <v>48</v>
+        <v>73.64</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="L7" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="M7" t="n">
-        <v>38.7</v>
+        <v>76.89</v>
       </c>
       <c r="N7" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>38.5</v>
+        <v>74.76</v>
       </c>
       <c r="P7" t="n">
-        <v>28.68</v>
+        <v>71.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>72.87</v>
+        <v>81.34</v>
       </c>
       <c r="R7" t="n">
-        <v>19.71</v>
+        <v>26.14</v>
       </c>
       <c r="S7" t="n">
-        <v>29.21</v>
+        <v>515.48</v>
       </c>
       <c r="T7" t="n">
-        <v>-9.49</v>
+        <v>-22.75</v>
       </c>
       <c r="U7" t="n">
-        <v>49.7</v>
+        <v>62.33571</v>
       </c>
       <c r="V7" t="n">
-        <v>49.7</v>
+        <v>436.35</v>
       </c>
       <c r="W7" t="n">
-        <v>-20.49</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-41.23</v>
+        <v>79.13</v>
+      </c>
+      <c r="X7" t="s">
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
-        <v>49.7</v>
+        <v>436.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>49.7</v>
+        <v>62.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>-20.49</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-41.23</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>80</v>
+        <v>79.13</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>90</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1774,81 +1966,81 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>24.42</v>
+        <v>33.42</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM7" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN7" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>359.12</v>
+        <v>341.47</v>
       </c>
       <c r="F8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.72</v>
+        <v>-0.72</v>
+      </c>
+      <c r="G8" t="s">
+        <v>96</v>
       </c>
       <c r="H8" t="n">
-        <v>352.8</v>
+        <v>341.4</v>
       </c>
       <c r="I8" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="J8" t="n">
-        <v>365.48</v>
+        <v>341.5</v>
       </c>
       <c r="K8" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="M8" t="n">
-        <v>356.56</v>
+        <v>342.19</v>
       </c>
       <c r="N8" t="n">
-        <v>361.1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>364.77</v>
+        <v>344.12</v>
       </c>
       <c r="P8" t="n">
-        <v>353.34</v>
+        <v>334.14</v>
       </c>
       <c r="Q8" t="n">
         <v>404.47</v>
       </c>
       <c r="R8" t="n">
-        <v>163.33</v>
+        <v>168.56</v>
       </c>
       <c r="S8" t="n">
-        <v>718.24</v>
+        <v>682.94</v>
       </c>
       <c r="T8" t="n">
-        <v>5.12</v>
+        <v>-1.44</v>
       </c>
       <c r="U8" t="n">
         <v>379.19</v>
@@ -1857,10 +2049,10 @@
         <v>758.38</v>
       </c>
       <c r="W8" t="n">
-        <v>-40.14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-5.29</v>
+        <v>-75.44</v>
+      </c>
+      <c r="X8" t="s">
+        <v>98</v>
       </c>
       <c r="Y8" t="n">
         <v>758.38</v>
@@ -1869,22 +2061,22 @@
         <v>379.19</v>
       </c>
       <c r="AA8" t="n">
-        <v>-40.14</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-5.29</v>
+        <v>-75.44</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>98</v>
       </c>
       <c r="AC8" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="AD8" t="n">
         <v>0.88</v>
       </c>
       <c r="AE8" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="n">
         <v>0.88</v>
@@ -1896,111 +2088,111 @@
         <v>28.84</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AK8" t="n">
         <v>1.23</v>
       </c>
       <c r="AL8" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AM8" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="AN8" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E9" t="n">
-        <v>921</v>
+        <v>792.75</v>
       </c>
       <c r="F9" t="n">
-        <v>31.41</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.53</v>
+        <v>-69.22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>107</v>
       </c>
       <c r="H9" t="n">
-        <v>920</v>
+        <v>792.87</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>922</v>
+        <v>793.24</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L9" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="M9" t="n">
-        <v>889.59</v>
+        <v>861.97</v>
       </c>
       <c r="N9" t="n">
-        <v>889.42</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>934.26</v>
+        <v>823.21</v>
       </c>
       <c r="P9" t="n">
-        <v>863</v>
+        <v>774.55</v>
       </c>
       <c r="Q9" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="R9" t="n">
-        <v>81.04</v>
+        <v>88.37</v>
       </c>
       <c r="S9" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="T9" t="n">
-        <v>62.82</v>
+        <v>-138.44</v>
       </c>
       <c r="U9" t="n">
         <v>874.63</v>
       </c>
       <c r="V9" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="W9" t="n">
-        <v>92.74</v>
-      </c>
-      <c r="X9" t="n">
-        <v>5.3</v>
+        <v>-163.76</v>
+      </c>
+      <c r="X9" t="s">
+        <v>112</v>
       </c>
       <c r="Y9" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="Z9" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="AA9" t="n">
-        <v>-474.08</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-20.47</v>
+        <v>-730.58</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>115</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2018,108 +2210,105 @@
         <v>1.47</v>
       </c>
       <c r="AL9" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="AM9" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="AN9" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>281.2</v>
+        <v>266.97</v>
       </c>
       <c r="F10" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.17</v>
+        <v>-14.29</v>
+      </c>
+      <c r="G10" t="s">
+        <v>121</v>
       </c>
       <c r="H10" t="n">
-        <v>281</v>
+        <v>266.98</v>
       </c>
       <c r="I10" t="n">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="J10" t="n">
-        <v>282</v>
+        <v>267.13</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="L10" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="M10" t="n">
-        <v>280.71</v>
+        <v>281.26</v>
       </c>
       <c r="N10" t="n">
-        <v>269.88</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>287.98</v>
+        <v>274.2</v>
       </c>
       <c r="P10" t="n">
-        <v>267.31</v>
+        <v>262.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>324.2</v>
+        <v>329.88</v>
       </c>
       <c r="R10" t="n">
         <v>61.44</v>
       </c>
       <c r="S10" t="n">
-        <v>281.2</v>
+        <v>800.91</v>
       </c>
       <c r="T10" t="n">
-        <v>0.49</v>
+        <v>-30.28</v>
       </c>
       <c r="U10" t="n">
-        <v>260.74</v>
+        <v>273.03667</v>
       </c>
       <c r="V10" t="n">
-        <v>260.74</v>
+        <v>819.11</v>
       </c>
       <c r="W10" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="X10" t="n">
-        <v>7.85</v>
+        <v>-18.2</v>
+      </c>
+      <c r="X10" t="s">
+        <v>123</v>
       </c>
       <c r="Y10" t="n">
-        <v>260.74</v>
+        <v>819.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>260.74</v>
+        <v>273.04</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>58</v>
+        <v>-18.2</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>123</v>
       </c>
       <c r="AD10" t="n">
         <v>0.24</v>
       </c>
       <c r="AE10" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="AF10" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="AG10" t="n">
         <v>0.24</v>
@@ -2137,105 +2326,105 @@
         <v>2.29</v>
       </c>
       <c r="AL10" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AM10" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="AN10" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" t="n">
-        <v>989.6</v>
+        <v>130</v>
+      </c>
+      <c r="E11" t="s">
+        <v>131</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.27</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="H11" t="n">
-        <v>989.5</v>
+        <v>-42.39</v>
+      </c>
+      <c r="G11" t="s">
+        <v>132</v>
+      </c>
+      <c r="H11" t="s">
+        <v>131</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>990</v>
+        <v>47</v>
+      </c>
+      <c r="J11" t="s">
+        <v>133</v>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="L11" t="s">
-        <v>114</v>
-      </c>
-      <c r="M11" t="n">
-        <v>995.87</v>
+        <v>134</v>
+      </c>
+      <c r="M11" t="s">
+        <v>135</v>
       </c>
       <c r="N11" t="n">
-        <v>971.81</v>
+        <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>115</v>
-      </c>
-      <c r="P11" t="n">
-        <v>960.2</v>
+        <v>136</v>
+      </c>
+      <c r="P11" t="s">
+        <v>137</v>
       </c>
       <c r="Q11" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="R11" t="n">
         <v>103.38</v>
       </c>
       <c r="S11" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="T11" t="n">
-        <v>-31.35</v>
-      </c>
-      <c r="U11" t="n">
-        <v>970.472</v>
+        <v>-243.13</v>
+      </c>
+      <c r="U11" t="s">
+        <v>140</v>
       </c>
       <c r="V11" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="W11" t="n">
-        <v>95.64</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.97</v>
+        <v>-8.87</v>
+      </c>
+      <c r="X11" t="s">
+        <v>142</v>
       </c>
       <c r="Y11" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="Z11" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="AA11" t="n">
-        <v>-928.36</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-15.8</v>
+        <v>-8.87</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>142</v>
       </c>
       <c r="AD11" t="n">
         <v>0.6</v>
       </c>
       <c r="AE11" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="AF11" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="n">
         <v>0.6</v>
@@ -2247,117 +2436,117 @@
         <v>24.42</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AK11" t="n">
         <v>2.17</v>
       </c>
       <c r="AL11" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AM11" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="AN11" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E12" t="n">
-        <v>844.13</v>
+        <v>150</v>
+      </c>
+      <c r="E12" t="s">
+        <v>151</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.61</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="H12" t="n">
-        <v>835</v>
+        <v>-84.58</v>
+      </c>
+      <c r="G12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H12" t="s">
+        <v>153</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>855</v>
+        <v>608</v>
+      </c>
+      <c r="J12" t="s">
+        <v>154</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>128</v>
-      </c>
-      <c r="M12" t="n">
-        <v>856.74</v>
+        <v>155</v>
+      </c>
+      <c r="M12" t="s">
+        <v>156</v>
       </c>
       <c r="N12" t="n">
-        <v>813.27</v>
-      </c>
-      <c r="O12" t="n">
-        <v>883</v>
-      </c>
-      <c r="P12" t="n">
-        <v>793.89</v>
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>157</v>
+      </c>
+      <c r="P12" t="s">
+        <v>158</v>
       </c>
       <c r="Q12" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="R12" t="n">
         <v>16.73</v>
       </c>
-      <c r="S12" t="n">
-        <v>844.13</v>
+      <c r="S12" t="s">
+        <v>151</v>
       </c>
       <c r="T12" t="n">
-        <v>-12.61</v>
-      </c>
-      <c r="U12" t="n">
-        <v>765.97</v>
-      </c>
-      <c r="V12" t="n">
-        <v>765.97</v>
+        <v>-84.58</v>
+      </c>
+      <c r="U12" t="s">
+        <v>160</v>
+      </c>
+      <c r="V12" t="s">
+        <v>160</v>
       </c>
       <c r="W12" t="n">
-        <v>78.16</v>
-      </c>
-      <c r="X12" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>765.97</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>765.97</v>
+        <v>87.12</v>
+      </c>
+      <c r="X12" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>160</v>
       </c>
       <c r="AA12" t="n">
-        <v>78.16</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>10.2</v>
+        <v>87.12</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>161</v>
       </c>
       <c r="AC12" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.32</v>
+        <v>4.6</v>
       </c>
       <c r="AE12" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="AF12" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.32</v>
+        <v>4.6</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2372,60 +2561,60 @@
         <v>10.56</v>
       </c>
       <c r="AL12" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E13" t="n">
-        <v>14.89</v>
+        <v>12.86</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5.66</v>
+        <v>-1.12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>168</v>
       </c>
       <c r="H13" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="I13" t="n">
-        <v>200</v>
+        <v>12.85</v>
+      </c>
+      <c r="I13" t="s">
+        <v>169</v>
       </c>
       <c r="J13" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="K13" t="n">
-        <v>30</v>
+        <v>12.86</v>
+      </c>
+      <c r="K13" t="s">
+        <v>170</v>
       </c>
       <c r="L13" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="M13" t="n">
-        <v>14.09</v>
+        <v>13.98</v>
       </c>
       <c r="N13" t="n">
-        <v>14.34</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>15.07</v>
+        <v>13.44</v>
       </c>
       <c r="P13" t="n">
-        <v>14.24</v>
+        <v>12.82</v>
       </c>
       <c r="Q13" t="n">
         <v>17.45</v>
@@ -2433,44 +2622,44 @@
       <c r="R13" t="n">
         <v>4</v>
       </c>
-      <c r="S13" t="n">
-        <v>595.48</v>
+      <c r="S13" t="s">
+        <v>172</v>
       </c>
       <c r="T13" t="n">
-        <v>31.88</v>
+        <v>-97.01</v>
       </c>
       <c r="U13" t="n">
-        <v>14.3225</v>
-      </c>
-      <c r="V13" t="n">
-        <v>572.9</v>
+        <v>13.72249</v>
+      </c>
+      <c r="V13" t="s">
+        <v>173</v>
       </c>
       <c r="W13" t="n">
-        <v>22.58</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>572.9</v>
+        <v>-103.51</v>
+      </c>
+      <c r="X13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>173</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.32</v>
+        <v>13.72</v>
       </c>
       <c r="AA13" t="n">
-        <v>22.58</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>3.94</v>
+        <v>-103.51</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>174</v>
       </c>
       <c r="AD13" t="n">
         <v>0.19</v>
       </c>
       <c r="AE13" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="AF13" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="AG13" t="n">
         <v>0.19</v>
@@ -2482,66 +2671,66 @@
         <v>46.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK13" t="n">
         <v>1.16</v>
       </c>
       <c r="AL13" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="AM13" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="AN13" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A14" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="E14" t="n">
-        <v>102.88</v>
+        <v>97.01</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.19</v>
+        <v>7.49</v>
+      </c>
+      <c r="G14" t="s">
+        <v>182</v>
       </c>
       <c r="H14" t="n">
-        <v>100.44</v>
+        <v>97</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>105.01</v>
+        <v>97.02</v>
       </c>
       <c r="K14" t="n">
-        <v>123</v>
+        <v>281</v>
       </c>
       <c r="L14" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="M14" t="n">
-        <v>103.08</v>
+        <v>89.52</v>
       </c>
       <c r="N14" t="n">
-        <v>103.38</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>103.38</v>
+        <v>97.59</v>
       </c>
       <c r="P14" t="n">
-        <v>98.43</v>
+        <v>90.22</v>
       </c>
       <c r="Q14" t="n">
         <v>211.48</v>
@@ -2550,10 +2739,10 @@
         <v>81.24</v>
       </c>
       <c r="S14" t="n">
-        <v>102.88</v>
+        <v>97.01</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2</v>
+        <v>7.49</v>
       </c>
       <c r="U14" t="n">
         <v>125.09</v>
@@ -2562,10 +2751,10 @@
         <v>125.09</v>
       </c>
       <c r="W14" t="n">
-        <v>-22.21</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-17.76</v>
+        <v>-28.09</v>
+      </c>
+      <c r="X14" t="s">
+        <v>184</v>
       </c>
       <c r="Y14" t="n">
         <v>125.09</v>
@@ -2574,22 +2763,22 @@
         <v>125.09</v>
       </c>
       <c r="AA14" t="n">
-        <v>-22.21</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-17.76</v>
+        <v>-28.09</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>184</v>
       </c>
       <c r="AC14" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -2598,7 +2787,7 @@
         <v>1.68</v>
       </c>
       <c r="AI14" t="n">
-        <v>52.63</v>
+        <v>17.42</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -2607,60 +2796,60 @@
         <v>0.94</v>
       </c>
       <c r="AL14" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="AM14" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="AN14" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A15" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="B15" t="n">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-1.03</v>
+        <v>0.61</v>
+      </c>
+      <c r="G15" t="s">
+        <v>191</v>
       </c>
       <c r="H15" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="I15" t="n">
-        <v>60</v>
+        <v>4.19</v>
+      </c>
+      <c r="I15" t="s">
+        <v>192</v>
       </c>
       <c r="J15" t="n">
-        <v>4.94</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="M15" t="n">
-        <v>4.85</v>
+        <v>3.59</v>
       </c>
       <c r="N15" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.89</v>
+        <v>4.24</v>
       </c>
       <c r="P15" t="n">
-        <v>4.4</v>
+        <v>3.66</v>
       </c>
       <c r="Q15" t="n">
         <v>29.01</v>
@@ -2669,10 +2858,10 @@
         <v>3.49</v>
       </c>
       <c r="S15" t="n">
-        <v>96</v>
+        <v>83.9</v>
       </c>
       <c r="T15" t="n">
-        <v>-1</v>
+        <v>12.1</v>
       </c>
       <c r="U15" t="n">
         <v>7.34</v>
@@ -2681,10 +2870,10 @@
         <v>146.8</v>
       </c>
       <c r="W15" t="n">
-        <v>-50.8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-34.6</v>
+        <v>-62.9</v>
+      </c>
+      <c r="X15" t="s">
+        <v>195</v>
       </c>
       <c r="Y15" t="n">
         <v>146.8</v>
@@ -2693,22 +2882,22 @@
         <v>7.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>-50.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-34.6</v>
+        <v>-62.9</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>195</v>
       </c>
       <c r="AC15" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -2726,72 +2915,72 @@
         <v>1.28</v>
       </c>
       <c r="AL15" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="AM15" t="s">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="AN15" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A16" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="E16" t="n">
-        <v>722.98</v>
+        <v>711.09</v>
       </c>
       <c r="F16" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.82</v>
+        <v>-5.29</v>
+      </c>
+      <c r="G16" t="s">
+        <v>201</v>
       </c>
       <c r="H16" t="n">
-        <v>723.12</v>
+        <v>711.02</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="J16" t="n">
-        <v>723.36</v>
+        <v>711.1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L16" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="M16" t="n">
-        <v>717.12</v>
+        <v>716.38</v>
       </c>
       <c r="N16" t="n">
-        <v>717.61</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>724.01</v>
+        <v>715.55</v>
       </c>
       <c r="P16" t="n">
-        <v>711.28</v>
+        <v>702.81</v>
       </c>
       <c r="Q16" t="n">
         <v>748.65</v>
       </c>
       <c r="R16" t="n">
-        <v>523.65</v>
+        <v>539.38</v>
       </c>
       <c r="S16" t="n">
-        <v>722.98</v>
+        <v>711.09</v>
       </c>
       <c r="T16" t="n">
-        <v>5.86</v>
+        <v>-5.29</v>
       </c>
       <c r="U16" t="n">
         <v>619.5</v>
@@ -2800,10 +2989,10 @@
         <v>619.5</v>
       </c>
       <c r="W16" t="n">
-        <v>103.48</v>
-      </c>
-      <c r="X16" t="n">
-        <v>16.7</v>
+        <v>91.59</v>
+      </c>
+      <c r="X16" t="s">
+        <v>203</v>
       </c>
       <c r="Y16" t="n">
         <v>619.5</v>
@@ -2812,25 +3001,25 @@
         <v>619.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>103.48</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>16.7</v>
+        <v>91.59</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>203</v>
       </c>
       <c r="AC16" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="AE16" t="s">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="AF16" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2839,78 +3028,78 @@
         <v>32.42</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="AK16" t="n">
         <v>1.23</v>
       </c>
       <c r="AL16" t="s">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="AM16" t="s">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="AN16" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="E17" t="n">
-        <v>61.47</v>
+        <v>53.58</v>
       </c>
       <c r="F17" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>211</v>
       </c>
       <c r="H17" t="n">
-        <v>57.5</v>
+        <v>53.58</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="J17" t="n">
-        <v>61.47</v>
-      </c>
-      <c r="K17" t="s">
-        <v>168</v>
+        <v>53.59</v>
+      </c>
+      <c r="K17" t="n">
+        <v>225</v>
       </c>
       <c r="L17" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="M17" t="n">
-        <v>60.82</v>
+        <v>52.36</v>
       </c>
       <c r="N17" t="n">
-        <v>60.53</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>61.83</v>
+        <v>53.87</v>
       </c>
       <c r="P17" t="n">
-        <v>59.87</v>
+        <v>52.46</v>
       </c>
       <c r="Q17" t="n">
         <v>109.83</v>
       </c>
       <c r="R17" t="n">
-        <v>32.06</v>
+        <v>32.49</v>
       </c>
       <c r="S17" t="n">
-        <v>184.41</v>
+        <v>160.74</v>
       </c>
       <c r="T17" t="n">
-        <v>1.95</v>
+        <v>3.66</v>
       </c>
       <c r="U17" t="n">
         <v>74.94667</v>
@@ -2919,10 +3108,10 @@
         <v>224.84</v>
       </c>
       <c r="W17" t="n">
-        <v>-40.43</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-17.98</v>
+        <v>-64.1</v>
+      </c>
+      <c r="X17" t="s">
+        <v>213</v>
       </c>
       <c r="Y17" t="n">
         <v>224.84</v>
@@ -2931,19 +3120,19 @@
         <v>74.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>-40.43</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-17.98</v>
+        <v>-64.1</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>213</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -2961,251 +3150,370 @@
         <v>0.45</v>
       </c>
       <c r="AL17" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="AM17" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="AN17" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A18" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>174</v>
-      </c>
-      <c r="E18" t="n">
-        <v>406.1</v>
+        <v>218</v>
+      </c>
+      <c r="E18" t="s">
+        <v>219</v>
       </c>
       <c r="F18" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="H18" t="n">
-        <v>406.01</v>
+        <v>-182.56</v>
+      </c>
+      <c r="G18" t="s">
+        <v>220</v>
+      </c>
+      <c r="H18" t="s">
+        <v>221</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
-      </c>
-      <c r="J18" t="n">
-        <v>406.1</v>
+        <v>5</v>
+      </c>
+      <c r="J18" t="s">
+        <v>222</v>
       </c>
       <c r="K18" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L18" t="s">
-        <v>175</v>
-      </c>
-      <c r="M18" t="n">
-        <v>399.15</v>
+        <v>223</v>
+      </c>
+      <c r="M18" t="s">
+        <v>224</v>
       </c>
       <c r="N18" t="n">
-        <v>399.46</v>
-      </c>
-      <c r="O18" t="n">
-        <v>406.68</v>
-      </c>
-      <c r="P18" t="n">
-        <v>386.76</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>498.83</v>
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>225</v>
+      </c>
+      <c r="P18" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>227</v>
       </c>
       <c r="R18" t="n">
-        <v>288.77</v>
-      </c>
-      <c r="S18" t="n">
-        <v>406.1</v>
+        <v>40.1</v>
+      </c>
+      <c r="S18" t="s">
+        <v>219</v>
       </c>
       <c r="T18" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="U18" t="n">
-        <v>468.88</v>
-      </c>
-      <c r="V18" t="n">
-        <v>468.88</v>
+        <v>10.52</v>
+      </c>
+      <c r="U18" t="s">
+        <v>228</v>
+      </c>
+      <c r="V18" t="s">
+        <v>229</v>
       </c>
       <c r="W18" t="n">
-        <v>-62.78</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-13.39</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>468.88</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>468.88</v>
+        <v>10.52</v>
+      </c>
+      <c r="X18" t="s">
+        <v>230</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>229</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>229</v>
       </c>
       <c r="AA18" t="n">
-        <v>-62.78</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-13.39</v>
+        <v>10.52</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>230</v>
       </c>
       <c r="AC18" t="s">
-        <v>176</v>
+        <v>231</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.09</v>
+        <v>29.48</v>
       </c>
       <c r="AI18" t="n">
-        <v>350.12</v>
+        <v>37.97</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.8</v>
+        <v>4.88</v>
       </c>
       <c r="AL18" t="s">
-        <v>177</v>
+        <v>232</v>
       </c>
       <c r="AM18" t="s">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="AN18" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" collapsed="0" hidden="0" customHeight="0" spans="1:1">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>181</v>
+        <v>236</v>
       </c>
       <c r="E19" t="n">
-        <v>682.68</v>
+        <v>383.09</v>
       </c>
       <c r="F19" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.66</v>
+        <v>7.97</v>
+      </c>
+      <c r="G19" t="s">
+        <v>237</v>
       </c>
       <c r="H19" t="n">
-        <v>682.4</v>
+        <v>382.98</v>
       </c>
       <c r="I19" t="n">
+        <v>65</v>
+      </c>
+      <c r="J19" t="n">
+        <v>383.09</v>
+      </c>
+      <c r="K19" t="n">
+        <v>40</v>
+      </c>
+      <c r="L19" t="s">
+        <v>238</v>
+      </c>
+      <c r="M19" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>387.8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>368.6</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>498.83</v>
+      </c>
+      <c r="R19" t="n">
+        <v>288.77</v>
+      </c>
+      <c r="S19" t="n">
+        <v>383.09</v>
+      </c>
+      <c r="T19" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="U19" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="V19" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-85.79</v>
+      </c>
+      <c r="X19" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>468.88</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-85.79</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>239</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>350.12</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>241</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>242</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="20" collapsed="0" hidden="0" customHeight="0" spans="1:1">
+      <c r="A20" t="s">
+        <v>244</v>
+      </c>
+      <c r="B20" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
-        <v>682.84</v>
-      </c>
-      <c r="K19" t="n">
-        <v>13</v>
-      </c>
-      <c r="L19" t="s">
-        <v>182</v>
-      </c>
-      <c r="M19" t="n">
-        <v>678.23</v>
-      </c>
-      <c r="N19" t="n">
-        <v>681.07</v>
-      </c>
-      <c r="O19" t="n">
-        <v>684.44</v>
-      </c>
-      <c r="P19" t="n">
-        <v>675.84</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="D20" t="s">
+        <v>245</v>
+      </c>
+      <c r="E20" t="n">
+        <v>673.91</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G20" t="s">
+        <v>246</v>
+      </c>
+      <c r="H20" t="n">
+        <v>673.87</v>
+      </c>
+      <c r="I20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J20" t="n">
+        <v>673.95</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="s">
+        <v>247</v>
+      </c>
+      <c r="M20" t="n">
+        <v>673.75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>676.96</v>
+      </c>
+      <c r="P20" t="n">
+        <v>668.14</v>
+      </c>
+      <c r="Q20" t="n">
         <v>699.15</v>
       </c>
-      <c r="R19" t="n">
-        <v>545.75</v>
-      </c>
-      <c r="S19" t="n">
-        <v>682.68</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="R20" t="n">
+        <v>558.34</v>
+      </c>
+      <c r="S20" t="n">
+        <v>673.91</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U20" t="n">
         <v>629.5</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V20" t="n">
         <v>629.5</v>
       </c>
-      <c r="W19" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="X19" t="n">
-        <v>8.45</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="W20" t="n">
+        <v>44.41</v>
+      </c>
+      <c r="X20" t="s">
+        <v>248</v>
+      </c>
+      <c r="Y20" t="n">
         <v>629.5</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z20" t="n">
         <v>629.5</v>
       </c>
-      <c r="AA19" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.45</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>160</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK19" t="n">
+      <c r="AA20" t="n">
+        <v>44.41</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>248</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>204</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>231</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1</v>
       </c>
-      <c r="AL19" t="s">
-        <v>183</v>
-      </c>
-      <c r="AM19" t="s">
-        <v>184</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>185</v>
+      <c r="AL20" t="s">
+        <v>249</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>250</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
